--- a/src/attributions/attributions_saliency_traj_161.xlsx
+++ b/src/attributions/attributions_saliency_traj_161.xlsx
@@ -999,3985 +999,3985 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0007621853146702051</v>
+        <v>8.383853128179908e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>0.003192765871062875</v>
+        <v>0.001437021885067225</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003321826225146651</v>
+        <v>0.0006145996158011258</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002410200890153646</v>
+        <v>0.001169805647805333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001351611805148423</v>
+        <v>0.0005162389716133475</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001759466249495745</v>
+        <v>0.0007673785439692438</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004524443065747619</v>
+        <v>0.0005312648136168718</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004467975522857159</v>
+        <v>0.000548092823009938</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001583779347129166</v>
+        <v>0.000199445043108426</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001027102232910693</v>
+        <v>7.093898602761328e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002479715505614877</v>
+        <v>0.001432222314178944</v>
       </c>
       <c r="L2" t="n">
-        <v>5.55837614228949e-05</v>
+        <v>0.0009246281115338206</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002021747175604105</v>
+        <v>0.001623965799808502</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004925835528410971</v>
+        <v>0.0003460634616203606</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001771601033397019</v>
+        <v>0.0007789612282067537</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0001902164076454937</v>
+        <v>0.0006848978227935731</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002295093727298081</v>
+        <v>0.0002327462134417146</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001372108701616526</v>
+        <v>4.194575740257278e-05</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001272818772122264</v>
+        <v>6.902120367158204e-05</v>
       </c>
       <c r="T2" t="n">
-        <v>4.661477214540355e-05</v>
+        <v>1.511347181804013e-05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005010304157622159</v>
+        <v>7.642302080057561e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001058522146195173</v>
+        <v>9.187644172925502e-05</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001143610337749124</v>
+        <v>2.628974107210524e-05</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0005334503948688507</v>
+        <v>0.0001989593147300184</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002351955627091229</v>
+        <v>0.0001292936503887177</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0004666664754040539</v>
+        <v>0.0004374017589725554</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0003565647639334202</v>
+        <v>0.0002634701086208224</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0002269246033392847</v>
+        <v>0.000104554055724293</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0002802932285703719</v>
+        <v>8.634642290417105e-05</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.542368985014036e-05</v>
+        <v>0.0002912428171839565</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.000543517991900444</v>
+        <v>0.000154936482431367</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0003818197292275727</v>
+        <v>9.695702465251088e-05</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.000601740728598088</v>
+        <v>0.0004359407466836274</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0006170349079184234</v>
+        <v>0.0002227040240541101</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0001211133494507521</v>
+        <v>0.0003208214184269309</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0007407303783111274</v>
+        <v>8.078690007096156e-05</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0003509477828629315</v>
+        <v>1.432860881322995e-05</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0005438677617348731</v>
+        <v>0.0003802854917012155</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0003323487762827426</v>
+        <v>0.0004087075358256698</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.495046545751393e-05</v>
+        <v>0.0002192632236983627</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0002979647542815655</v>
+        <v>0.0002678784367162734</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0002057650126516819</v>
+        <v>0.0002872894110623747</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00040209642611444</v>
+        <v>0.0001756219135131687</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0001939561770996079</v>
+        <v>1.588457962498069e-05</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0007885415107011795</v>
+        <v>7.405044743791223e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.901696229353547e-05</v>
+        <v>0.000138517512823455</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.001989344600588083</v>
+        <v>0.0004453436413314193</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0002894852659665048</v>
+        <v>0.0002791483129840344</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.001127176568843424</v>
+        <v>0.0006639605853706598</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.001617291709408164</v>
+        <v>0.0007635113433934748</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0009553376585245132</v>
+        <v>0.0005037660012021661</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.001382159069180489</v>
+        <v>1.244153463630937e-05</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.00166804576292634</v>
+        <v>0.0001101430534617975</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.001034080400131643</v>
+        <v>0.0002101024438161403</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0004430323897395283</v>
+        <v>0.0001456605095881969</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0003876090049743652</v>
+        <v>0.0002117646799888462</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0003979417961090803</v>
+        <v>0.0004258110711816698</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.238256850745529e-05</v>
+        <v>0.0001228761248057708</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0005425726412795484</v>
+        <v>0.0005143358721397817</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0002673508424777538</v>
+        <v>0.0002787569246720523</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0006511902320198715</v>
+        <v>0.0001625377917662263</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0001258261472685263</v>
+        <v>0.0005626393249258399</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.001463263877667487</v>
+        <v>0.0002876869984902442</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0001122491448768415</v>
+        <v>2.097931428579614e-05</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.395566793391481e-05</v>
+        <v>0.0001949456927832216</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.819159559905529e-05</v>
+        <v>7.485956302843988e-06</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0001909162965603173</v>
+        <v>9.055780537892133e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.000219456895138137</v>
+        <v>0.0003142010536976159</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.081509253708646e-05</v>
+        <v>0.0001617293310118839</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0005042636767029762</v>
+        <v>8.715226613276172e-06</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0003388498444110155</v>
+        <v>0.0001555665949126706</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0003680222143884748</v>
+        <v>7.76821980252862e-05</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.261599188903347e-05</v>
+        <v>9.806029993342236e-05</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.001173193799331784</v>
+        <v>0.0003565868828445673</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0003005870385095477</v>
+        <v>0.0002807527780532837</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.001224113395437598</v>
+        <v>0.0005527894245460629</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0004387912922538817</v>
+        <v>0.0001833622518461198</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0003480073646642268</v>
+        <v>0.0003374673251528293</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.000721234711818397</v>
+        <v>0.0001602610718691722</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0005052694468759</v>
+        <v>0.000126804516185075</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.000610358314588666</v>
+        <v>0.0001656393142184243</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0002042615378741175</v>
+        <v>0.0001002922435873188</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0004711536748800427</v>
+        <v>0.0004403479397296906</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0003668428980745375</v>
+        <v>7.957930210977793e-05</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0003199498169124126</v>
+        <v>0.0004603529814630747</v>
       </c>
       <c r="CH2" t="n">
-        <v>3.437901250435971e-05</v>
+        <v>0.0002104649029206485</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.000323026004480198</v>
+        <v>0.0001280002761632204</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0001894240122055635</v>
+        <v>8.853544386511203e-06</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0001059308706317097</v>
+        <v>4.286614421289414e-05</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0003621600044425577</v>
+        <v>1.148098817793652e-06</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.0002354577300138772</v>
+        <v>0.0001915527536766604</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0001850103435572237</v>
+        <v>2.761331415968016e-05</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0002752436848822981</v>
+        <v>0.0005696602165699005</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0004131605383008718</v>
+        <v>0.0007188367890194058</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.0002768355770967901</v>
+        <v>1.602097472641617e-05</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0001170221075881273</v>
+        <v>0.000283665198367089</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0008898220839910209</v>
+        <v>0.0001848439424065873</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.0004772852989844978</v>
+        <v>0.0003962893679272383</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0001096231426345184</v>
+        <v>4.979362711310387e-05</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.000171083229361102</v>
+        <v>8.758811600273475e-05</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0004837981832679361</v>
+        <v>0.0004404139763209969</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0003066982899326831</v>
+        <v>0.0001499696081737056</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0004150174208916724</v>
+        <v>0.0004622964188456535</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0001747217611409724</v>
+        <v>0.0001020948693621904</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0003630522987805307</v>
+        <v>0.000160239142132923</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0002475111978128552</v>
+        <v>4.417335367179476e-05</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.000202369294129312</v>
+        <v>2.634063093864825e-05</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0002747215621639043</v>
+        <v>8.691223047208041e-05</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0002244877978228033</v>
+        <v>0.000250969547778368</v>
       </c>
       <c r="DF2" t="n">
-        <v>9.079747542273253e-05</v>
+        <v>0.0002620357554405928</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.135623774142005e-05</v>
+        <v>0.0003025905461981893</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.001339847454801202</v>
+        <v>0.0004274231032468379</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.001907444908283651</v>
+        <v>0.0001302680175285786</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.001525387517176569</v>
+        <v>0.001014914363622665</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.0006508053047582507</v>
+        <v>1.212952338391915e-05</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.0005861171521246433</v>
+        <v>0.0006454503163695335</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0005827404675073922</v>
+        <v>3.315581125207245e-05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.0002695014991331846</v>
+        <v>0.0001337424037046731</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0004385561624076217</v>
+        <v>0.0002005808637477458</v>
       </c>
       <c r="DP2" t="n">
-        <v>6.547241355292499e-05</v>
+        <v>0.0001047752011800185</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0005428524455055594</v>
+        <v>0.0004877630271948874</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0003810627968050539</v>
+        <v>8.926079317461699e-06</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0002554324164520949</v>
+        <v>2.900624895119108e-05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.000238195774727501</v>
+        <v>0.0002401289239060134</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0001250579371117055</v>
+        <v>0.0001450501586077735</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0009673198219388723</v>
+        <v>0.0004158829688094556</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0001261901488760486</v>
+        <v>1.202885687234811e-05</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0003228419518563896</v>
+        <v>1.752470780047588e-05</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0007157991058193147</v>
+        <v>0.0003455433761700988</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0003444424946792424</v>
+        <v>0.0002024139976128936</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0005741830100305378</v>
+        <v>5.56057711946778e-05</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0004674540250562131</v>
+        <v>0.0002972034562844783</v>
       </c>
       <c r="EC2" t="n">
-        <v>6.466794002335519e-05</v>
+        <v>4.221667404635809e-05</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0003380415146239102</v>
+        <v>0.0007978292996995151</v>
       </c>
       <c r="EE2" t="n">
-        <v>7.41353869671002e-05</v>
+        <v>0.0007427911623381078</v>
       </c>
       <c r="EF2" t="n">
-        <v>3.260286757722497e-05</v>
+        <v>0.0002897750237025321</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0002214246487710625</v>
+        <v>0.000245872390223667</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0003083824994973838</v>
+        <v>0.0002128178894054145</v>
       </c>
       <c r="EI2" t="n">
-        <v>6.115136056905612e-05</v>
+        <v>0.0003912054526153952</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0003449560899753124</v>
+        <v>5.402241731644608e-05</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0004583342524711043</v>
+        <v>1.084651739802212e-05</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.0001821763289626688</v>
+        <v>3.254184048273601e-05</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.759493898134679e-06</v>
+        <v>9.566574590280652e-05</v>
       </c>
       <c r="EN2" t="n">
-        <v>8.516992966178805e-05</v>
+        <v>1.673000951996073e-05</v>
       </c>
       <c r="EO2" t="n">
-        <v>4.209396138321608e-05</v>
+        <v>0.0001095582701964304</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0004196684458293021</v>
+        <v>0.0005428162403404713</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.0001365600182907656</v>
+        <v>1.075941690942273e-05</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.0002427266736049205</v>
+        <v>0.0001353175903204829</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0002550560748204589</v>
+        <v>0.0001527527201687917</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.0009215833269990981</v>
+        <v>5.281241465127096e-05</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.0008246777579188347</v>
+        <v>0.0001887810649350286</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.001161356340162456</v>
+        <v>5.73289071326144e-05</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.0002034742210526019</v>
+        <v>0.0003196022589690983</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0001841334305936471</v>
+        <v>9.726796270115301e-05</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.0003977841115556657</v>
+        <v>0.0004309056093916297</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0002051276969723403</v>
+        <v>0.000109906613943167</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0005081715062260628</v>
+        <v>0.0005411467282101512</v>
       </c>
       <c r="FB2" t="n">
-        <v>7.652687781956047e-05</v>
+        <v>0.0001538539218017831</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0003710280579980463</v>
+        <v>0.0001282737648580223</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0003842470759991556</v>
+        <v>6.076697536627762e-05</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.000149971543578431</v>
+        <v>8.278045424958691e-05</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0004246035241521895</v>
+        <v>0.0001147334987763315</v>
       </c>
       <c r="FG2" t="n">
-        <v>7.489595736842602e-05</v>
+        <v>3.113079583272338e-05</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0003468047652859241</v>
+        <v>0.0001364572817692533</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0002850878809113055</v>
+        <v>7.302576250367565e-07</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0004616778460331261</v>
+        <v>0.0002005233836825937</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0006370030459947884</v>
+        <v>0.0003299613017588854</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0001809844252420589</v>
+        <v>0.0001666328171268106</v>
       </c>
       <c r="FM2" t="n">
-        <v>8.118644473142922e-05</v>
+        <v>0.0001545263075968251</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.0006942555191926658</v>
+        <v>0.0001872130669653416</v>
       </c>
       <c r="FO2" t="n">
-        <v>7.283974809979554e-06</v>
+        <v>0.0001968925062101334</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0001704194146441296</v>
+        <v>0.0004140172968618572</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0002227848599432036</v>
+        <v>0.0007032515713945031</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.0002436402282910421</v>
+        <v>0.000238760098000057</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0003259321674704552</v>
+        <v>0.0005253212875686586</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.0009569905232638121</v>
+        <v>0.000657630676869303</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0008877174695953727</v>
+        <v>0.0001516503398306668</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.001012574415653944</v>
+        <v>0.0001106355484807864</v>
       </c>
       <c r="FW2" t="n">
-        <v>6.106711953179911e-05</v>
+        <v>0.000346825981978327</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0003344828437548131</v>
+        <v>0.0006032299133948982</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0002986147883348167</v>
+        <v>2.698406751733273e-05</v>
       </c>
       <c r="FZ2" t="n">
-        <v>5.558574775932357e-05</v>
+        <v>1.571338361827657e-05</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0005188646027818322</v>
+        <v>6.491260137408972e-05</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0001742602617014199</v>
+        <v>0.0005659493617713451</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0009333251509815454</v>
+        <v>0.0001352420949842781</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.0001995826751226559</v>
+        <v>8.286120282718912e-05</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.001428575487807393</v>
+        <v>0.0004262241127435118</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.000796644773799926</v>
+        <v>2.172009089917992e-06</v>
       </c>
       <c r="GG2" t="n">
-        <v>7.986182026797906e-06</v>
+        <v>0.0002692978596314788</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.04056696221232414</v>
+        <v>1.01393525255844e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.08051758259534836</v>
+        <v>6.63697937852703e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00629636412486434</v>
+        <v>7.047895451250952e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>0.017839714884758</v>
+        <v>4.652643110603094e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05405119061470032</v>
+        <v>8.100964805635158e-06</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02528710290789604</v>
+        <v>2.322933323739562e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005093182437121868</v>
+        <v>2.788419078569859e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01012969948351383</v>
+        <v>1.236020762007684e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02861353568732738</v>
+        <v>9.598158612789121e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03661021590232849</v>
+        <v>1.75337445398327e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08499186486005783</v>
+        <v>5.012013207306154e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02011789940297604</v>
+        <v>1.283136225538328e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00113458838313818</v>
+        <v>7.147731230361387e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02689390070736408</v>
+        <v>2.923254942288622e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004644363187253475</v>
+        <v>1.096081086870981e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003610909217968583</v>
+        <v>2.807711280183867e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002246816642582417</v>
+        <v>3.324219142086804e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01896023936569691</v>
+        <v>1.108799006033223e-05</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006484736688435078</v>
+        <v>1.615790097275749e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009863981977105141</v>
+        <v>1.272726058232365e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02611654438078403</v>
+        <v>5.442619567475049e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02571039833128452</v>
+        <v>9.431588296138216e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03091612458229065</v>
+        <v>1.738034370646346e-05</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02201184630393982</v>
+        <v>1.406324645358836e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004044205415993929</v>
+        <v>4.052317308378406e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006774672772735357</v>
+        <v>4.502769115788396e-06</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004412955604493618</v>
+        <v>1.522146612842334e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02399885468184948</v>
+        <v>1.224196330440463e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02251199632883072</v>
+        <v>7.429064680763986e-06</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.01583565957844257</v>
+        <v>3.219891823391663e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.02774599194526672</v>
+        <v>7.796868885634467e-06</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.020273108035326</v>
+        <v>1.088748103938997e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03164748474955559</v>
+        <v>1.738876926538069e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02615112438797951</v>
+        <v>8.010800229385495e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.03760571032762527</v>
+        <v>2.840982961060945e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.02304750867187977</v>
+        <v>6.510610091936542e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.00771423103287816</v>
+        <v>9.155701263807714e-07</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.003303424455225468</v>
+        <v>1.876027090474963e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01010614447295666</v>
+        <v>4.530258138402132e-06</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.007564525119960308</v>
+        <v>4.381592134450329e-06</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.00977411400526762</v>
+        <v>2.067186187559855e-06</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.01237846910953522</v>
+        <v>5.442985184345162e-06</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.002347238129004836</v>
+        <v>7.631366315763444e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01467137038707733</v>
+        <v>2.18337845581118e-06</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.01655031368136406</v>
+        <v>8.403452739003114e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.01222121994942427</v>
+        <v>1.148565047515149e-06</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.02849731035530567</v>
+        <v>2.669828973012045e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.002058596583083272</v>
+        <v>1.469164317313698e-06</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.06012840569019318</v>
+        <v>1.23076570162084e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.03451589122414589</v>
+        <v>6.852114165667444e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.02339235693216324</v>
+        <v>2.789277004922042e-06</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.01685486920177937</v>
+        <v>8.389361028093845e-08</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.02221652306616306</v>
+        <v>3.582462886697613e-05</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.009838017635047436</v>
+        <v>8.123794941639062e-06</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0462656058371067</v>
+        <v>1.603211603651289e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.002168704057112336</v>
+        <v>1.649998011998832e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.01009400002658367</v>
+        <v>2.726602815528167e-06</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.01690640673041344</v>
+        <v>3.000593551405473e-06</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.07347490638494492</v>
+        <v>2.738140392466448e-05</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.002745958510786295</v>
+        <v>1.184741995530203e-05</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003908894490450621</v>
+        <v>1.163676733995089e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0192161425948143</v>
+        <v>3.557444506441243e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01678447797894478</v>
+        <v>1.043886913976166e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.01433683279901743</v>
+        <v>2.010027856158558e-06</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.02698271162807941</v>
+        <v>6.047130227671005e-06</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01625813171267509</v>
+        <v>2.12358418139047e-06</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.03988189250230789</v>
+        <v>5.070318820799002e-06</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.006572038866579533</v>
+        <v>9.877448974293657e-06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.003143681678920984</v>
+        <v>2.413336733297911e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.02130692824721336</v>
+        <v>1.826811285354779e-06</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.008409867063164711</v>
+        <v>1.490289650973864e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.003155452199280262</v>
+        <v>9.29315501707606e-06</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.01190879940986633</v>
+        <v>4.123038706893567e-06</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.02564819343388081</v>
+        <v>2.360348662477918e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.01672976277768612</v>
+        <v>6.500741619674955e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.005248809698969126</v>
+        <v>2.127759216818959e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.02243968099355698</v>
+        <v>2.848530675692018e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.02518996223807335</v>
+        <v>2.226597098342609e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.004974318668246269</v>
+        <v>1.141019856731873e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.01219468005001545</v>
+        <v>1.532587884867098e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.006760057061910629</v>
+        <v>7.017563348199474e-06</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.003929699305444956</v>
+        <v>4.163399353274144e-06</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.01965291425585747</v>
+        <v>1.309529579884838e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.004148701671510935</v>
+        <v>4.284153874323238e-06</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.003201107494533062</v>
+        <v>1.504629017290426e-05</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0007149364100769162</v>
+        <v>9.803301281863241e-07</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.004388770088553429</v>
+        <v>9.851138202066068e-06</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.01650969311594963</v>
+        <v>1.881521711766254e-07</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01153267920017242</v>
+        <v>7.245343567774398e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.00817052461206913</v>
+        <v>8.400497790717054e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.000841932836920023</v>
+        <v>1.085173607862089e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01477646082639694</v>
+        <v>3.750307541849907e-06</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.004327301867306232</v>
+        <v>1.606419027666561e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.033378966152668</v>
+        <v>3.595541056711227e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001302274875342846</v>
+        <v>2.170395964640193e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01092292461544275</v>
+        <v>1.871985659818165e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.007429013960063457</v>
+        <v>4.88622072225553e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.002382196485996246</v>
+        <v>7.253224794112612e-06</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.009549876675009727</v>
+        <v>4.779746632266324e-06</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.008570626378059387</v>
+        <v>5.792733645648696e-06</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.01720303297042847</v>
+        <v>1.161819091066718e-05</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.006183474790304899</v>
+        <v>5.833994691784028e-06</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.007460074964910746</v>
+        <v>1.648494617256802e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.004541631788015366</v>
+        <v>3.69054851034889e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01086283009499311</v>
+        <v>1.019125556922518e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.02042962610721588</v>
+        <v>3.025055548278033e-07</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.004918640479445457</v>
+        <v>8.356902071682271e-06</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.008640570566058159</v>
+        <v>9.791953743842896e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0004545352421700954</v>
+        <v>1.705396061879583e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.02769108489155769</v>
+        <v>2.361417500651442e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.03911939635872841</v>
+        <v>2.701504490687512e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.006068333983421326</v>
+        <v>2.121811121469364e-05</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05494233965873718</v>
+        <v>1.01338619060698e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.05130128562450409</v>
+        <v>2.383734863542486e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.02141506038606167</v>
+        <v>1.255152801604709e-05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.01281477510929108</v>
+        <v>6.140605819382472e-06</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.007526649627834558</v>
+        <v>1.859992698882706e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.01186898350715637</v>
+        <v>2.94172650683322e-06</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.00308276666328311</v>
+        <v>3.771933506868663e-06</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01754061691462994</v>
+        <v>8.772829460212961e-06</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.005283340811729431</v>
+        <v>7.576262760267127e-06</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02472353726625443</v>
+        <v>2.5847521101241e-06</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.03159420937299728</v>
+        <v>1.007098217087332e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.004144700244069099</v>
+        <v>9.321560355601832e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.006216718815267086</v>
+        <v>1.473047905165004e-05</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.01695129089057446</v>
+        <v>1.879577393992804e-05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.007950389757752419</v>
+        <v>8.107058420137037e-06</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.00418535340577364</v>
+        <v>1.142703149525914e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.006583466194570065</v>
+        <v>1.463890475861263e-05</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.001110989600419998</v>
+        <v>1.572392284288071e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.03265997022390366</v>
+        <v>3.330076879137778e-06</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.01116511877626181</v>
+        <v>1.365509342576843e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01225301902741194</v>
+        <v>1.891002511911211e-06</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.005432385951280594</v>
+        <v>1.594637797097676e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.004629045724868774</v>
+        <v>1.372416704725765e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.01095570344477892</v>
+        <v>1.842572237364948e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.01174854673445225</v>
+        <v>8.817131856631022e-06</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.002726363483816385</v>
+        <v>1.568545030750101e-06</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.02109090983867645</v>
+        <v>1.093144146580016e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.004161954857409</v>
+        <v>1.007569971989142e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.008995137177407742</v>
+        <v>2.142366975022014e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.009763590060174465</v>
+        <v>1.919976284625591e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.01902851089835167</v>
+        <v>8.597827218181919e-06</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.01739979162812233</v>
+        <v>1.001446889858926e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.01660945080220699</v>
+        <v>3.787234163610265e-06</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0275750532746315</v>
+        <v>1.034200067806523e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.02796152047812939</v>
+        <v>5.863156729901675e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.001266798935830593</v>
+        <v>9.689870239526499e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.02422014251351357</v>
+        <v>7.62622403271962e-06</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.04328569397330284</v>
+        <v>8.165665121850907e-07</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.03007199987769127</v>
+        <v>1.257704752788413e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.01821992918848991</v>
+        <v>1.906086936287466e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.007855456322431564</v>
+        <v>6.702734935970511e-06</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.001806401181966066</v>
+        <v>4.610334144672379e-06</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.02058093622326851</v>
+        <v>1.385376890539192e-05</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.009528930298984051</v>
+        <v>3.915661636710865e-06</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.005492471624165773</v>
+        <v>2.003347617574036e-05</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.005263881757855415</v>
+        <v>1.064535126715782e-07</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.01129472069442272</v>
+        <v>8.076248377619777e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.01292243599891663</v>
+        <v>3.225349246349651e-06</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.002604929730296135</v>
+        <v>6.735253464285051e-06</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.01174393482506275</v>
+        <v>6.676333214272745e-06</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.001606279285624623</v>
+        <v>3.974060746259056e-06</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.005506291054189205</v>
+        <v>7.711343641858548e-06</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.000540941720828414</v>
+        <v>1.004596379061695e-05</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.0340520478785038</v>
+        <v>4.491021172725596e-06</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.03132985532283783</v>
+        <v>3.259659251853009e-06</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.005106275901198387</v>
+        <v>1.640005939407274e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.001238692551851273</v>
+        <v>2.855172169802245e-07</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.01723599061369896</v>
+        <v>1.252715355803957e-05</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.01260379515588284</v>
+        <v>2.982926616823534e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.009577217511832714</v>
+        <v>1.341386450803839e-05</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.06049118191003799</v>
+        <v>1.567613981023896e-05</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.03764831274747849</v>
+        <v>5.952490027993917e-06</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.04350897669792175</v>
+        <v>1.973428516066633e-05</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.07492902874946594</v>
+        <v>1.487570443714503e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.007685105782002211</v>
+        <v>1.77266283571953e-05</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.03998517990112305</v>
+        <v>2.552770274633076e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.0166197344660759</v>
+        <v>4.501378043642035e-07</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.01256953831762075</v>
+        <v>5.706812225980684e-05</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.03625530004501343</v>
+        <v>4.018776962766424e-06</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.00518626207485795</v>
+        <v>8.869807970768306e-06</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.01926572434604168</v>
+        <v>1.773629992385395e-05</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.01359886303544044</v>
+        <v>1.960177360160742e-05</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.00508161773905158</v>
+        <v>1.040968345478177e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.02754123695194721</v>
+        <v>6.071093139325967e-06</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.02882258594036102</v>
+        <v>3.717935396707617e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.00917263887822628</v>
+        <v>1.5718429494882e-05</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.02142645232379436</v>
+        <v>4.40909388998989e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.839740424562478e-08</v>
+        <v>1.362779494229471e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>5.552201969294401e-07</v>
+        <v>7.580329111078754e-05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.778236935479072e-07</v>
+        <v>2.345064785913564e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>2.892074633109587e-07</v>
+        <v>2.954180672531947e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>8.951963081926806e-07</v>
+        <v>1.682917354628444e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.571602751937462e-06</v>
+        <v>8.307774260174483e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.070837470251718e-06</v>
+        <v>2.309943010914139e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>9.629018222767627e-07</v>
+        <v>2.901153857237659e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>1.712734160719265e-06</v>
+        <v>2.029674033110496e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.568198169683455e-07</v>
+        <v>3.397393356863176e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>3.321417523238779e-07</v>
+        <v>9.574630530551076e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>2.723148782024509e-07</v>
+        <v>3.371480124769732e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.401881005198447e-08</v>
+        <v>1.602738848305307e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.254988092114218e-06</v>
+        <v>1.448310831619892e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>9.871941983874422e-07</v>
+        <v>8.555974636692554e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.974314554649027e-07</v>
+        <v>3.775672439587652e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.156606211035978e-07</v>
+        <v>1.044356486090692e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>5.724812695007131e-07</v>
+        <v>2.901620428019669e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63737803152253e-07</v>
+        <v>5.159414513400407e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.544057965929824e-07</v>
+        <v>1.036718185787322e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>3.068536784667231e-07</v>
+        <v>1.132117449742509e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>8.94801246431598e-08</v>
+        <v>1.125123617384816e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.351563469143002e-06</v>
+        <v>1.799620258680079e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>5.311779318617482e-07</v>
+        <v>4.509930931817507e-06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27860971588234e-07</v>
+        <v>9.524290362605825e-06</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.839085707113554e-07</v>
+        <v>1.117923966376111e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.926379907985392e-07</v>
+        <v>5.782883818028495e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.024001304334888e-07</v>
+        <v>6.091365776228486e-07</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.00217516774137e-06</v>
+        <v>4.458687271835515e-06</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.694611218132195e-07</v>
+        <v>9.770742508408148e-06</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.176632384973345e-07</v>
+        <v>3.939119778806344e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.309936919824395e-06</v>
+        <v>1.429338135494618e-05</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.117262785210187e-08</v>
+        <v>3.734437268576585e-05</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.542343721273937e-07</v>
+        <v>2.291521468578139e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.810891358734807e-07</v>
+        <v>6.12262447248213e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.404841658673831e-07</v>
+        <v>1.097022686735727e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.823986934823552e-07</v>
+        <v>2.183303195124608e-06</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.908416713078623e-07</v>
+        <v>1.40835782076465e-05</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.17225519349995e-07</v>
+        <v>1.052225888997782e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.799049406756239e-07</v>
+        <v>1.475488716096152e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.215177462654538e-06</v>
+        <v>5.567449079535436e-06</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.996938175987452e-07</v>
+        <v>1.247104046342429e-05</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.829977236411651e-07</v>
+        <v>3.171598564222222e-06</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.032646537169057e-06</v>
+        <v>1.727927337924484e-05</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.303326761601056e-08</v>
+        <v>2.797569777612807e-06</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.224923261768708e-07</v>
+        <v>1.195956429000944e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.818152193474816e-07</v>
+        <v>7.521326187998056e-05</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.434307475596142e-07</v>
+        <v>2.239989589725155e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.126120410954172e-07</v>
+        <v>3.650640337582445e-06</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.089367515305639e-06</v>
+        <v>3.333903441671282e-05</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.643691689423576e-06</v>
+        <v>5.950537160970271e-05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.70111433009879e-07</v>
+        <v>7.097770321706776e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.306439571635565e-06</v>
+        <v>9.723010407469701e-06</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.087776682761614e-08</v>
+        <v>7.426524462061934e-07</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.256608553352635e-07</v>
+        <v>2.001673919949098e-06</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.961524832149735e-07</v>
+        <v>2.426110995656927e-06</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.84905478717701e-07</v>
+        <v>1.878552029666025e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.876898920727399e-07</v>
+        <v>1.592895387148019e-06</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.442013285668509e-06</v>
+        <v>2.030873656622134e-05</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.46296088132658e-06</v>
+        <v>1.406481987942243e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.303513244010901e-07</v>
+        <v>1.111144410970155e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2.266817489271489e-07</v>
+        <v>3.807876419159584e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.170227103055367e-07</v>
+        <v>1.526728374301456e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>5.355090593184286e-08</v>
+        <v>3.290994527560542e-06</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.181131304103474e-07</v>
+        <v>1.623083699087147e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.394076817490713e-08</v>
+        <v>3.245982043154072e-07</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.300409593341101e-07</v>
+        <v>1.581575270392932e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.43652840733921e-08</v>
+        <v>2.058914105873555e-05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.165446512160997e-07</v>
+        <v>2.797600791382138e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>5.345102636056254e-07</v>
+        <v>2.0879828298348e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.717656286677084e-07</v>
+        <v>9.176315870718099e-06</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.126391907746438e-06</v>
+        <v>2.123855301761068e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.457429329500883e-07</v>
+        <v>6.283838501985883e-06</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.630885861914066e-07</v>
+        <v>4.761178206535988e-05</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.621054082079354e-07</v>
+        <v>8.712007911526598e-06</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.297219114348991e-07</v>
+        <v>2.18540481000673e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.594256435870193e-07</v>
+        <v>3.333144377393182e-06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.357149521183601e-07</v>
+        <v>2.87121074507013e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.229534317166326e-07</v>
+        <v>1.270855682378169e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.516659484783304e-07</v>
+        <v>5.144943770574173e-06</v>
       </c>
       <c r="CC4" t="n">
-        <v>7.31560987787816e-07</v>
+        <v>7.781351087032817e-06</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.348523710476002e-07</v>
+        <v>5.158347448741551e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.82144319182953e-07</v>
+        <v>2.38242373598041e-05</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.431090979053806e-08</v>
+        <v>2.842539061020943e-06</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.23982545119361e-07</v>
+        <v>6.585110440937569e-06</v>
       </c>
       <c r="CH4" t="n">
-        <v>6.352803438858245e-08</v>
+        <v>5.221848368819337e-06</v>
       </c>
       <c r="CI4" t="n">
-        <v>3.001186712481285e-07</v>
+        <v>1.74478700500913e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>9.071430895346566e-08</v>
+        <v>1.347672878182493e-06</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.357098966536796e-08</v>
+        <v>1.69499116964289e-07</v>
       </c>
       <c r="CL4" t="n">
-        <v>3.422288159526943e-07</v>
+        <v>3.54555686499225e-06</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.519731824828341e-07</v>
+        <v>1.394750142935663e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>4.814716021428467e-07</v>
+        <v>2.837207284756005e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>3.644402113422984e-09</v>
+        <v>2.379053876211401e-05</v>
       </c>
       <c r="CP4" t="n">
-        <v>4.840729843635927e-07</v>
+        <v>1.211372273246525e-05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.148469891631976e-06</v>
+        <v>4.265202733222395e-07</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.177689227915835e-06</v>
+        <v>4.199122486170381e-06</v>
       </c>
       <c r="CS4" t="n">
-        <v>5.854110440850491e-07</v>
+        <v>2.204968404839747e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.112098170277022e-07</v>
+        <v>1.353074276266852e-05</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.42777582823328e-06</v>
+        <v>3.753841610887321e-06</v>
       </c>
       <c r="CV4" t="n">
-        <v>9.190529226543731e-08</v>
+        <v>1.582914592290763e-06</v>
       </c>
       <c r="CW4" t="n">
-        <v>3.749709165390414e-08</v>
+        <v>2.072892311844043e-05</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.040154700149287e-07</v>
+        <v>4.830727903026855e-06</v>
       </c>
       <c r="CY4" t="n">
-        <v>9.810803192067397e-08</v>
+        <v>5.014225735067157e-06</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.816505511622381e-08</v>
+        <v>1.560688360768836e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.090946426529626e-07</v>
+        <v>1.877016802609432e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>5.895057597626874e-08</v>
+        <v>3.946324341086438e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.291852041480524e-08</v>
+        <v>1.147442048932135e-06</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.664413614184014e-07</v>
+        <v>2.487449819454923e-06</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.77700854919749e-07</v>
+        <v>1.178626280307071e-05</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.595332375676662e-07</v>
+        <v>1.994393278437201e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.607710942153062e-08</v>
+        <v>1.221918500959873e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>2.745986193986028e-07</v>
+        <v>1.338768925052136e-06</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.923242507473333e-07</v>
+        <v>6.270893209148198e-06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>9.192772267851979e-07</v>
+        <v>4.718497802969068e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.932771619474806e-07</v>
+        <v>3.993181053374428e-06</v>
       </c>
       <c r="DL4" t="n">
-        <v>8.079037456809601e-07</v>
+        <v>2.330484676349442e-05</v>
       </c>
       <c r="DM4" t="n">
-        <v>2.442567392790806e-08</v>
+        <v>1.894591696327552e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>2.117245543331592e-07</v>
+        <v>3.366327746334719e-06</v>
       </c>
       <c r="DO4" t="n">
-        <v>4.06094898153242e-07</v>
+        <v>1.542074278404471e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.684550382691668e-07</v>
+        <v>7.093345175235299e-06</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.530913777969545e-07</v>
+        <v>1.787976361811161e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.196156404148496e-06</v>
+        <v>6.531213330163155e-06</v>
       </c>
       <c r="DS4" t="n">
-        <v>7.137267630241695e-07</v>
+        <v>9.67507094173925e-06</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.28312194647151e-07</v>
+        <v>9.453819984628353e-06</v>
       </c>
       <c r="DU4" t="n">
-        <v>5.230309625403606e-07</v>
+        <v>1.284326754102949e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.388177276519855e-07</v>
+        <v>4.402157173899468e-06</v>
       </c>
       <c r="DW4" t="n">
-        <v>4.122822190311126e-07</v>
+        <v>4.268326392775634e-06</v>
       </c>
       <c r="DX4" t="n">
-        <v>2.134615044724342e-07</v>
+        <v>3.342529453220777e-06</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.142492630558991e-07</v>
+        <v>1.368129778711591e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.151485887225135e-07</v>
+        <v>3.747214805116528e-06</v>
       </c>
       <c r="EA4" t="n">
-        <v>5.278207595438289e-07</v>
+        <v>2.313656477781478e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>6.168037316456321e-07</v>
+        <v>1.095873449230567e-05</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.217273108977679e-07</v>
+        <v>3.977224878326524e-06</v>
       </c>
       <c r="ED4" t="n">
-        <v>3.549470193320303e-07</v>
+        <v>2.401182609901298e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>5.085341285848699e-07</v>
+        <v>2.572892117314041e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.935508180395118e-07</v>
+        <v>6.768601451767609e-06</v>
       </c>
       <c r="EG4" t="n">
-        <v>1.496850217108658e-07</v>
+        <v>2.136522653017892e-06</v>
       </c>
       <c r="EH4" t="n">
-        <v>2.830265088960005e-08</v>
+        <v>7.685011951252818e-06</v>
       </c>
       <c r="EI4" t="n">
-        <v>9.433619538867788e-07</v>
+        <v>9.539617167320102e-06</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.010700287906729e-07</v>
+        <v>1.124403388530482e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.93755340660573e-08</v>
+        <v>2.96085340778518e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>3.877925678352767e-07</v>
+        <v>4.235527740092948e-06</v>
       </c>
       <c r="EM4" t="n">
-        <v>1.185013331905793e-07</v>
+        <v>8.231659194279928e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>2.035567945313232e-07</v>
+        <v>4.931160219712183e-06</v>
       </c>
       <c r="EO4" t="n">
-        <v>3.926880935978261e-07</v>
+        <v>1.387246015838173e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>7.491494784517272e-07</v>
+        <v>1.354512824036647e-05</v>
       </c>
       <c r="EQ4" t="n">
-        <v>3.877367475979554e-07</v>
+        <v>8.08592994872015e-06</v>
       </c>
       <c r="ER4" t="n">
-        <v>1.383847916258674e-07</v>
+        <v>2.311017851752695e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>4.381360270144796e-07</v>
+        <v>3.759371975320391e-05</v>
       </c>
       <c r="ET4" t="n">
-        <v>5.748566422880685e-07</v>
+        <v>2.435062742733862e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>8.391289441078698e-08</v>
+        <v>1.549895387142897e-06</v>
       </c>
       <c r="EV4" t="n">
-        <v>5.545656449612579e-07</v>
+        <v>1.346541830571368e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>3.255712499594665e-07</v>
+        <v>1.333538784820121e-05</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.758995153977594e-07</v>
+        <v>3.144225502182962e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>8.995838385317256e-08</v>
+        <v>2.494625732651912e-05</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1.066688426476503e-07</v>
+        <v>3.516597189445747e-06</v>
       </c>
       <c r="FA4" t="n">
-        <v>1.078462190662322e-07</v>
+        <v>2.949121153505985e-06</v>
       </c>
       <c r="FB4" t="n">
-        <v>1.233799729050133e-08</v>
+        <v>7.472668585251085e-06</v>
       </c>
       <c r="FC4" t="n">
-        <v>3.625136173468491e-07</v>
+        <v>1.592850821907632e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>4.332574121690413e-08</v>
+        <v>3.347456413393957e-06</v>
       </c>
       <c r="FE4" t="n">
-        <v>7.60230989271804e-08</v>
+        <v>3.60315561920288e-06</v>
       </c>
       <c r="FF4" t="n">
-        <v>1.969781635580148e-07</v>
+        <v>4.43810858996585e-06</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.832780469612771e-07</v>
+        <v>4.536032520263689e-06</v>
       </c>
       <c r="FH4" t="n">
-        <v>6.377255772349599e-07</v>
+        <v>1.842796700657345e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>3.514278148486483e-07</v>
+        <v>1.652536775509361e-05</v>
       </c>
       <c r="FJ4" t="n">
-        <v>2.171910011838918e-07</v>
+        <v>1.633340434636921e-05</v>
       </c>
       <c r="FK4" t="n">
-        <v>8.299456339955213e-07</v>
+        <v>1.577768671268132e-07</v>
       </c>
       <c r="FL4" t="n">
-        <v>2.126733420482196e-07</v>
+        <v>2.591920383565594e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>6.323516998918421e-08</v>
+        <v>5.540834536077455e-06</v>
       </c>
       <c r="FN4" t="n">
-        <v>3.460465904936427e-07</v>
+        <v>1.684321978245862e-05</v>
       </c>
       <c r="FO4" t="n">
-        <v>1.873548995945384e-07</v>
+        <v>4.093458119314164e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.484599003262701e-07</v>
+        <v>7.916370122984517e-06</v>
       </c>
       <c r="FQ4" t="n">
-        <v>1.550883013123894e-07</v>
+        <v>4.314289071771782e-06</v>
       </c>
       <c r="FR4" t="n">
-        <v>4.386071168482886e-07</v>
+        <v>2.313654840691015e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>3.342823333696288e-07</v>
+        <v>7.97660686657764e-06</v>
       </c>
       <c r="FT4" t="n">
-        <v>6.171304107738251e-07</v>
+        <v>9.723886250867508e-06</v>
       </c>
       <c r="FU4" t="n">
-        <v>7.0270476726364e-07</v>
+        <v>8.7443786469521e-06</v>
       </c>
       <c r="FV4" t="n">
-        <v>6.028419647918781e-07</v>
+        <v>1.288064322579885e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>3.792548852743494e-07</v>
+        <v>4.514732427196577e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>4.497812255976896e-08</v>
+        <v>2.299126754223835e-05</v>
       </c>
       <c r="FY4" t="n">
-        <v>5.49816945749626e-07</v>
+        <v>1.09314596556942e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>6.493682462860306e-07</v>
+        <v>4.221732524456456e-06</v>
       </c>
       <c r="GA4" t="n">
-        <v>7.032672328932676e-07</v>
+        <v>2.024231434916146e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.039448077084671e-08</v>
+        <v>8.165522558556404e-06</v>
       </c>
       <c r="GC4" t="n">
-        <v>7.222834597087058e-08</v>
+        <v>3.453264071140438e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>2.895441184591618e-07</v>
+        <v>3.230943184462376e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.44373370858375e-06</v>
+        <v>5.600191343546612e-06</v>
       </c>
       <c r="GF4" t="n">
-        <v>9.018857554110582e-07</v>
+        <v>4.720736797025893e-07</v>
       </c>
       <c r="GG4" t="n">
-        <v>1.237230549122614e-06</v>
+        <v>1.360996338917175e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8.046745278988965e-06</v>
+        <v>8.908393647288904e-05</v>
       </c>
       <c r="B5" t="n">
-        <v>3.559796459740028e-05</v>
+        <v>0.001204573083668947</v>
       </c>
       <c r="C5" t="n">
-        <v>2.774772156044492e-06</v>
+        <v>0.0002888420422095805</v>
       </c>
       <c r="D5" t="n">
-        <v>1.843367317633238e-05</v>
+        <v>0.0006655142642557621</v>
       </c>
       <c r="E5" t="n">
-        <v>4.840079327550484e-06</v>
+        <v>6.913129618624225e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.133055957325269e-05</v>
+        <v>0.0005588162457570434</v>
       </c>
       <c r="G5" t="n">
-        <v>7.402339861073415e-07</v>
+        <v>0.0002546909381635487</v>
       </c>
       <c r="H5" t="n">
-        <v>3.914803073712392e-06</v>
+        <v>0.0002030903706327081</v>
       </c>
       <c r="I5" t="n">
-        <v>3.830296918749809e-06</v>
+        <v>0.0001330075901933014</v>
       </c>
       <c r="J5" t="n">
-        <v>9.721334208734334e-06</v>
+        <v>6.928496532054851e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>2.206859244324733e-05</v>
+        <v>0.00126648775767535</v>
       </c>
       <c r="L5" t="n">
-        <v>8.811416023490892e-07</v>
+        <v>0.0004252602520864457</v>
       </c>
       <c r="M5" t="n">
-        <v>2.101296740875114e-05</v>
+        <v>0.0008960487903095782</v>
       </c>
       <c r="N5" t="n">
-        <v>1.138713378168177e-05</v>
+        <v>0.0003646737313829362</v>
       </c>
       <c r="O5" t="n">
-        <v>1.673896804277319e-05</v>
+        <v>0.0004966767155565321</v>
       </c>
       <c r="P5" t="n">
-        <v>6.125987965788227e-07</v>
+        <v>0.0002602771273814142</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.145463314373046e-07</v>
+        <v>4.37477501691319e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>5.539928679354489e-06</v>
+        <v>0.0002291145792696625</v>
       </c>
       <c r="S5" t="n">
-        <v>2.673747303560958e-07</v>
+        <v>6.478361683548428e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>3.682361011669855e-06</v>
+        <v>5.772993063146714e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>4.348089532868471e-07</v>
+        <v>4.212836938677356e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>5.05848265675013e-06</v>
+        <v>4.56323687103577e-05</v>
       </c>
       <c r="W5" t="n">
-        <v>3.15333500111592e-06</v>
+        <v>0.0001153069315478206</v>
       </c>
       <c r="X5" t="n">
-        <v>3.976581865572371e-06</v>
+        <v>0.0002743194345384836</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.249530320521444e-06</v>
+        <v>0.0001301632146351039</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.103743670682888e-06</v>
+        <v>0.00016076720203273</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.761099949566415e-06</v>
+        <v>0.000179032635060139</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.134156264015473e-06</v>
+        <v>0.0001055720058502629</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.146303581364919e-06</v>
+        <v>3.780666156671941e-05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.391328282807081e-06</v>
+        <v>0.0001314532855758443</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.059088046735269e-06</v>
+        <v>0.0001478115154895931</v>
       </c>
       <c r="AF5" t="n">
-        <v>5.002565558243077e-06</v>
+        <v>0.0001146754293586127</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.683655904751504e-06</v>
+        <v>0.0004925996181555092</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.927565674326615e-07</v>
+        <v>9.888770000543445e-05</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.376483510284743e-06</v>
+        <v>0.0001350332458969206</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.265888833288045e-07</v>
+        <v>8.656093268655241e-05</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.051814817605191e-06</v>
+        <v>1.682150468695909e-06</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.046632627956569e-06</v>
+        <v>0.0003316671936772764</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.22530041785285e-07</v>
+        <v>0.0001570417953189462</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.192292059698957e-07</v>
+        <v>0.0002170205843867734</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.823111794394208e-06</v>
+        <v>0.000161962365382351</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.922423275071196e-06</v>
+        <v>0.0001631127815926448</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.383038807034609e-06</v>
+        <v>7.188555900938809e-05</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.266605179102044e-07</v>
+        <v>1.705550312181003e-05</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.209982312706416e-06</v>
+        <v>7.705530879320577e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.482158134233032e-07</v>
+        <v>3.776701123570092e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.331069117644802e-05</v>
+        <v>0.0006377149256877601</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.165337948805245e-06</v>
+        <v>0.0001857822935562581</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.490129529382102e-06</v>
+        <v>0.0002559387648943812</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.280974970541138e-06</v>
+        <v>0.0005751962889917195</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.094820163416443e-06</v>
+        <v>0.0003559288161341101</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.72283079236513e-06</v>
+        <v>1.494786192779429e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.903299673562287e-06</v>
+        <v>7.946556434035301e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.164227114713867e-06</v>
+        <v>3.276772622484714e-05</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.530363639787538e-06</v>
+        <v>6.676759221591055e-05</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.50110075387056e-06</v>
+        <v>8.936868835007772e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.740613232774194e-06</v>
+        <v>0.0002439704403514042</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.732501565740677e-06</v>
+        <v>6.708345608785748e-06</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.559529421996558e-06</v>
+        <v>0.0002966366009786725</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.029869721009163e-06</v>
+        <v>0.0001635335793253034</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.569512728063273e-06</v>
+        <v>0.0001429337135050446</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6.91718469170155e-08</v>
+        <v>0.0001533987378934398</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.158301974006463e-06</v>
+        <v>0.0001277677365578711</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.785484412015649e-06</v>
+        <v>4.695674579124898e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.852576810459141e-06</v>
+        <v>0.0001135561979026534</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.690246449470578e-06</v>
+        <v>5.211971711105434e-06</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.068596247932874e-06</v>
+        <v>0.0001066792319761589</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.621124051278457e-06</v>
+        <v>0.0001058113266481087</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.728933850448811e-06</v>
+        <v>5.702235284843482e-06</v>
       </c>
       <c r="BR5" t="n">
-        <v>2.550083081587218e-06</v>
+        <v>3.246125925215892e-05</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.629967851447873e-09</v>
+        <v>6.43570238025859e-05</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.823418870117166e-06</v>
+        <v>2.503744326531887e-06</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.227185960800853e-07</v>
+        <v>2.929627953562886e-07</v>
       </c>
       <c r="BV5" t="n">
-        <v>1.157839778898051e-05</v>
+        <v>0.0004901592037640512</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.726764594423003e-06</v>
+        <v>0.0001353391271550208</v>
       </c>
       <c r="BX5" t="n">
-        <v>5.107870947540505e-06</v>
+        <v>0.000321884814184159</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.134578719254932e-06</v>
+        <v>5.555432653636672e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>5.462886747409357e-06</v>
+        <v>0.0003231264126952738</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.088031467588735e-06</v>
+        <v>0.0001459843333577737</v>
       </c>
       <c r="CB5" t="n">
-        <v>1.265339960809797e-06</v>
+        <v>2.725777812884189e-05</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.648305780894589e-06</v>
+        <v>0.0001664660667302087</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.340012088097865e-06</v>
+        <v>2.275119186379015e-05</v>
       </c>
       <c r="CE5" t="n">
-        <v>5.514675649465062e-06</v>
+        <v>0.0003910181694664061</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.031824578807573e-06</v>
+        <v>5.03284900332801e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>1.495190872446983e-06</v>
+        <v>0.0002631694660522044</v>
       </c>
       <c r="CH5" t="n">
-        <v>9.482207588007441e-07</v>
+        <v>1.047952719090972e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.791675797197968e-06</v>
+        <v>0.0001238437544088811</v>
       </c>
       <c r="CJ5" t="n">
-        <v>8.203325023714569e-07</v>
+        <v>3.233294410165399e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>2.116013320119237e-07</v>
+        <v>2.708193460421171e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>3.495888449833728e-07</v>
+        <v>4.526968950813171e-06</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.70170744695497e-06</v>
+        <v>9.17551078600809e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.393162491098337e-07</v>
+        <v>0.0002683669445104897</v>
       </c>
       <c r="CO5" t="n">
-        <v>2.448914528940804e-06</v>
+        <v>0.0003851545334327966</v>
       </c>
       <c r="CP5" t="n">
-        <v>4.06720619139378e-06</v>
+        <v>0.0003988167736679316</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.176437081085169e-06</v>
+        <v>1.240354322362691e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>5.117785349284532e-06</v>
+        <v>0.0001885790261439979</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.823036877292907e-06</v>
+        <v>4.315619662520476e-05</v>
       </c>
       <c r="CT5" t="n">
-        <v>7.979697329574265e-06</v>
+        <v>2.104512532241642e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.048203216669208e-06</v>
+        <v>4.466139580472372e-05</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.931106226038537e-06</v>
+        <v>5.16141972184414e-06</v>
       </c>
       <c r="CW5" t="n">
-        <v>4.093068582733395e-06</v>
+        <v>0.0003707778523676097</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.843041331994755e-06</v>
+        <v>7.944165554363281e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.549290229580947e-06</v>
+        <v>0.0002662250190041959</v>
       </c>
       <c r="CZ5" t="n">
-        <v>5.031562295698677e-07</v>
+        <v>7.979004294611514e-05</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.827570369845489e-06</v>
+        <v>0.0001379968744004145</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.168072344626125e-06</v>
+        <v>1.987758878385648e-05</v>
       </c>
       <c r="DC5" t="n">
-        <v>7.796694490025402e-07</v>
+        <v>2.574821519374382e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.19812170851219e-07</v>
+        <v>4.437516327016056e-05</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.215557969975634e-06</v>
+        <v>7.978195208124816e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>6.881063200125936e-06</v>
+        <v>0.0003225286200176924</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.208442313327396e-06</v>
+        <v>9.059700460056774e-06</v>
       </c>
       <c r="DH5" t="n">
-        <v>7.436100531776901e-06</v>
+        <v>0.0002654472773429006</v>
       </c>
       <c r="DI5" t="n">
-        <v>3.83173892259947e-06</v>
+        <v>0.0001689387572696432</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.865076683316147e-06</v>
+        <v>0.00054712756536901</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.55086127051618e-06</v>
+        <v>1.805806641641539e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>6.362763542711036e-07</v>
+        <v>0.0004193280474282801</v>
       </c>
       <c r="DM5" t="n">
-        <v>5.589752163359663e-07</v>
+        <v>0.000208857876714319</v>
       </c>
       <c r="DN5" t="n">
-        <v>4.658759280573577e-06</v>
+        <v>2.684869286895264e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.032672339031706e-06</v>
+        <v>0.0002124584425473586</v>
       </c>
       <c r="DP5" t="n">
-        <v>2.640734010128654e-06</v>
+        <v>1.359946327283978e-05</v>
       </c>
       <c r="DQ5" t="n">
-        <v>4.2359133658465e-06</v>
+        <v>0.0001819738245103508</v>
       </c>
       <c r="DR5" t="n">
-        <v>1.985921244340716e-06</v>
+        <v>4.094943506061099e-05</v>
       </c>
       <c r="DS5" t="n">
-        <v>4.086436092620715e-06</v>
+        <v>7.813723641447723e-05</v>
       </c>
       <c r="DT5" t="n">
-        <v>1.388948930980405e-06</v>
+        <v>0.0001615695509826764</v>
       </c>
       <c r="DU5" t="n">
-        <v>7.217869324449566e-08</v>
+        <v>8.049637108342722e-05</v>
       </c>
       <c r="DV5" t="n">
-        <v>1.737294496706454e-06</v>
+        <v>0.0003224647080060095</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.631255031497858e-06</v>
+        <v>6.872523226775229e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>4.128318096263683e-07</v>
+        <v>0.0001003912111627869</v>
       </c>
       <c r="DY5" t="n">
-        <v>4.127622560190503e-06</v>
+        <v>0.000236901018070057</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.240219484723639e-06</v>
+        <v>0.0001464419619878754</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.754735305643408e-06</v>
+        <v>1.293200148211326e-05</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.090810997084191e-06</v>
+        <v>0.0002545877068769187</v>
       </c>
       <c r="EC5" t="n">
-        <v>9.580439552792086e-08</v>
+        <v>4.875146260019392e-07</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.876951728263521e-06</v>
+        <v>0.0004298716958146542</v>
       </c>
       <c r="EE5" t="n">
-        <v>6.70690099013882e-07</v>
+        <v>0.0004452785942703485</v>
       </c>
       <c r="EF5" t="n">
-        <v>2.678561941138469e-07</v>
+        <v>6.01965730311349e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>2.680126954146544e-06</v>
+        <v>0.0002528621116653085</v>
       </c>
       <c r="EH5" t="n">
-        <v>8.307100074489426e-08</v>
+        <v>0.0001607978774700314</v>
       </c>
       <c r="EI5" t="n">
-        <v>6.733647524015396e-07</v>
+        <v>0.000206670185434632</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.329226279267459e-06</v>
+        <v>0.0001108912329073064</v>
       </c>
       <c r="EK5" t="n">
-        <v>2.488808604539372e-06</v>
+        <v>0.0001095349434763193</v>
       </c>
       <c r="EL5" t="n">
-        <v>2.540083187341224e-06</v>
+        <v>4.125596024096012e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.867514129116898e-06</v>
+        <v>4.207706297165714e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>9.331098453913e-07</v>
+        <v>7.527767593273893e-05</v>
       </c>
       <c r="EO5" t="n">
-        <v>2.499397851352114e-06</v>
+        <v>6.538948946399614e-05</v>
       </c>
       <c r="EP5" t="n">
-        <v>3.899647708749399e-06</v>
+        <v>0.0003283323021605611</v>
       </c>
       <c r="EQ5" t="n">
-        <v>3.063420308535569e-07</v>
+        <v>2.132527151843533e-05</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.386548996786587e-06</v>
+        <v>0.0001743112807162106</v>
       </c>
       <c r="ES5" t="n">
-        <v>2.97892847811454e-06</v>
+        <v>2.484971992089413e-05</v>
       </c>
       <c r="ET5" t="n">
-        <v>1.219104251504177e-05</v>
+        <v>2.278542524436489e-06</v>
       </c>
       <c r="EU5" t="n">
-        <v>4.41200245404616e-06</v>
+        <v>7.911045395303518e-05</v>
       </c>
       <c r="EV5" t="n">
-        <v>1.786479515430983e-06</v>
+        <v>0.00010453570575919</v>
       </c>
       <c r="EW5" t="n">
-        <v>8.144070307025686e-09</v>
+        <v>0.0001677446562098339</v>
       </c>
       <c r="EX5" t="n">
-        <v>1.555431481392588e-06</v>
+        <v>2.981834404636174e-05</v>
       </c>
       <c r="EY5" t="n">
-        <v>4.572208581521409e-06</v>
+        <v>0.0004167274164501578</v>
       </c>
       <c r="EZ5" t="n">
-        <v>6.360373845382128e-07</v>
+        <v>5.620325828203931e-05</v>
       </c>
       <c r="FA5" t="n">
-        <v>2.268848220410291e-06</v>
+        <v>0.0003020795702468604</v>
       </c>
       <c r="FB5" t="n">
-        <v>6.022140723871416e-07</v>
+        <v>2.102177177221165e-06</v>
       </c>
       <c r="FC5" t="n">
-        <v>4.013588295492809e-06</v>
+        <v>0.0001447231916245073</v>
       </c>
       <c r="FD5" t="n">
-        <v>1.836609499150654e-06</v>
+        <v>2.325932655367069e-06</v>
       </c>
       <c r="FE5" t="n">
-        <v>2.526421667425893e-07</v>
+        <v>4.452774010132998e-05</v>
       </c>
       <c r="FF5" t="n">
-        <v>6.152162086436874e-07</v>
+        <v>7.856929732952267e-05</v>
       </c>
       <c r="FG5" t="n">
-        <v>1.31516947021737e-06</v>
+        <v>5.433706246549264e-05</v>
       </c>
       <c r="FH5" t="n">
-        <v>1.315265421908407e-06</v>
+        <v>0.0001473428419558331</v>
       </c>
       <c r="FI5" t="n">
-        <v>5.530778253159951e-07</v>
+        <v>1.550985689391382e-05</v>
       </c>
       <c r="FJ5" t="n">
-        <v>2.002027713388088e-06</v>
+        <v>8.954716759035364e-05</v>
       </c>
       <c r="FK5" t="n">
-        <v>8.269925046988646e-07</v>
+        <v>6.064278568373993e-05</v>
       </c>
       <c r="FL5" t="n">
-        <v>1.043876522999199e-06</v>
+        <v>3.069098602281883e-05</v>
       </c>
       <c r="FM5" t="n">
-        <v>2.485139248165069e-06</v>
+        <v>2.790228609228507e-05</v>
       </c>
       <c r="FN5" t="n">
-        <v>2.271302719236701e-07</v>
+        <v>0.0001054006570484489</v>
       </c>
       <c r="FO5" t="n">
-        <v>1.574996758790803e-06</v>
+        <v>0.0001045639801304787</v>
       </c>
       <c r="FP5" t="n">
-        <v>2.249606723125908e-08</v>
+        <v>0.0001509854919277132</v>
       </c>
       <c r="FQ5" t="n">
-        <v>4.704762886831304e-06</v>
+        <v>0.000222994844079949</v>
       </c>
       <c r="FR5" t="n">
-        <v>4.076122195328935e-07</v>
+        <v>0.0002458882518112659</v>
       </c>
       <c r="FS5" t="n">
-        <v>2.521421947676572e-06</v>
+        <v>0.0001860390475485474</v>
       </c>
       <c r="FT5" t="n">
-        <v>6.500878043880221e-06</v>
+        <v>0.000466889439849183</v>
       </c>
       <c r="FU5" t="n">
-        <v>2.527275910324533e-06</v>
+        <v>2.021556065301411e-05</v>
       </c>
       <c r="FV5" t="n">
-        <v>2.515839923944441e-06</v>
+        <v>6.561896589118987e-05</v>
       </c>
       <c r="FW5" t="n">
-        <v>1.403686383127933e-06</v>
+        <v>0.0001785568601917475</v>
       </c>
       <c r="FX5" t="n">
-        <v>2.977980329887941e-06</v>
+        <v>0.0001717882551020011</v>
       </c>
       <c r="FY5" t="n">
-        <v>3.034724841199932e-06</v>
+        <v>0.0001303525205003098</v>
       </c>
       <c r="FZ5" t="n">
-        <v>2.18178320210427e-06</v>
+        <v>0.0001594724162714556</v>
       </c>
       <c r="GA5" t="n">
-        <v>1.693715603323653e-07</v>
+        <v>0.0001344881311524659</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.95672123481927e-06</v>
+        <v>0.0002555274404585361</v>
       </c>
       <c r="GC5" t="n">
-        <v>2.487720848876052e-06</v>
+        <v>6.161401870485861e-06</v>
       </c>
       <c r="GD5" t="n">
-        <v>3.12850625050487e-06</v>
+        <v>0.0002055180812021717</v>
       </c>
       <c r="GE5" t="n">
-        <v>5.336494723451324e-06</v>
+        <v>0.0002281904307892546</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.532459691588883e-06</v>
+        <v>3.260783705627546e-05</v>
       </c>
       <c r="GG5" t="n">
-        <v>4.657825911635882e-07</v>
+        <v>8.621429878985509e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0003403050941415131</v>
+        <v>0.002798046451061964</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001885386998765171</v>
+        <v>0.01612468436360359</v>
       </c>
       <c r="C6" t="n">
-        <v>3.781990380957723e-05</v>
+        <v>0.001116748433560133</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001506710657849908</v>
+        <v>0.001581353135406971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003848642809316516</v>
+        <v>0.0008166952757164836</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001921448041684926</v>
+        <v>0.01204090192914009</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000617417914327234</v>
+        <v>0.001428116345778108</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002999726566486061</v>
+        <v>0.01207459159195423</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001092658727429807</v>
+        <v>0.00427802000194788</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005724237998947501</v>
+        <v>0.001068601850420237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009520540479570627</v>
+        <v>0.01804433576762676</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001176024743472226</v>
+        <v>0.002856412203982472</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00191292236559093</v>
+        <v>0.002159944269806147</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009245725814253092</v>
+        <v>0.007619686424732208</v>
       </c>
       <c r="O6" t="n">
-        <v>0.002368380082771182</v>
+        <v>0.01581127941608429</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0006750879110768437</v>
+        <v>0.0007957962807267904</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.45105610601604e-05</v>
+        <v>0.008352601900696754</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0005836784839630127</v>
+        <v>0.01114390697330236</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002381287922617048</v>
+        <v>0.0003302231198176742</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000471544306492433</v>
+        <v>0.001572413719259202</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003731734468601644</v>
+        <v>0.002664610277861357</v>
       </c>
       <c r="V6" t="n">
-        <v>9.488288196735084e-05</v>
+        <v>0.002294006524607539</v>
       </c>
       <c r="W6" t="n">
-        <v>1.680845343798865e-05</v>
+        <v>0.002907183719798923</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0001925076066982001</v>
+        <v>0.0004645153821911663</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002901561965700239</v>
+        <v>0.002441911259666085</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001551762397866696</v>
+        <v>0.0007358860457316041</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.942664524307474e-05</v>
+        <v>0.001725961803458631</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001830596011132002</v>
+        <v>0.0002585212932899594</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0008561419090256095</v>
+        <v>0.0005719966720789671</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0003227863053325564</v>
+        <v>0.0008273933199234307</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0007512578740715981</v>
+        <v>0.002008260460570455</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.00110023352317512</v>
+        <v>0.004596727900207043</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003564113867469132</v>
+        <v>0.006913188844919205</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0001116837811423466</v>
+        <v>0.00032047662534751</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.717051004059613e-05</v>
+        <v>0.00738611863926053</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0001461541978642344</v>
+        <v>0.001127987634390593</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.000113470436190255</v>
+        <v>2.586690243333578e-05</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0004200726107228547</v>
+        <v>0.003484207671135664</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0001445641828468069</v>
+        <v>0.003238428384065628</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0002589579380583018</v>
+        <v>0.001216155709698796</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.892323729814962e-05</v>
+        <v>0.0003329467726871371</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001587562292115763</v>
+        <v>0.004143283236771822</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0002747491525951773</v>
+        <v>0.0001521200174465775</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0003987367963418365</v>
+        <v>0.0001149113522842526</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0002471460320521146</v>
+        <v>0.0003865630133077502</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0005347876576706767</v>
+        <v>0.002333325566723943</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0014150949427858</v>
+        <v>0.01081965677440166</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0001644075382500887</v>
+        <v>0.00609948392957449</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0006680744700133801</v>
+        <v>0.001843842677772045</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0002891898038797081</v>
+        <v>0.01078390516340733</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.001031802617944777</v>
+        <v>0.01231225579977036</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0007684134179726243</v>
+        <v>0.004863669164478779</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0003038614231627434</v>
+        <v>0.001388035947456956</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0009064939222298563</v>
+        <v>0.001472123665735126</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0004171372856944799</v>
+        <v>0.002043364103883505</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0004569037701003253</v>
+        <v>0.003330831881612539</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0003361979324836284</v>
+        <v>0.001947219367139041</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0004477423499338329</v>
+        <v>0.000562980305403471</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001146671012975276</v>
+        <v>0.00489247590303421</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0006558887544088066</v>
+        <v>0.001063127187080681</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0002848323783837259</v>
+        <v>0.002662585116922855</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0003523411287460476</v>
+        <v>0.01162899844348431</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0002340550563530996</v>
+        <v>0.0007502568187192082</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0002369523281231523</v>
+        <v>0.001139394473284483</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.494127253768966e-05</v>
+        <v>0.001272052177228034</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0001203869178425521</v>
+        <v>0.001634352258406579</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0002229836100013927</v>
+        <v>0.001569272018969059</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0001677718391874805</v>
+        <v>0.004418683238327503</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0001650210178922862</v>
+        <v>0.003314164932817221</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0008350933203473687</v>
+        <v>0.002328002126887441</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0002383514074608684</v>
+        <v>0.0009599468321539462</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0004818371380679309</v>
+        <v>0.003585201688110828</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0002522882132325321</v>
+        <v>0.0009861330036073923</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0006265246192924678</v>
+        <v>0.007336865644901991</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0003568860120140016</v>
+        <v>0.002762003801763058</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0003319057868793607</v>
+        <v>0.005598606076091528</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0005907734157517552</v>
+        <v>0.002502801595255733</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0004271622165106237</v>
+        <v>0.006429973524063826</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0001448244147468358</v>
+        <v>0.001089917728677392</v>
       </c>
       <c r="CB6" t="n">
-        <v>7.661017298232764e-05</v>
+        <v>0.001520778751000762</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0004108841239940375</v>
+        <v>0.003237525932490826</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.504226646735333e-05</v>
+        <v>0.0001454245357308537</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0004453689907677472</v>
+        <v>0.005304275546222925</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0002685417712200433</v>
+        <v>0.0005270598921924829</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0002705190563574433</v>
+        <v>0.0003510641399770975</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0001169682000181638</v>
+        <v>0.0004002614878118038</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0002681766054593027</v>
+        <v>0.003210676833987236</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0002707985113374889</v>
+        <v>0.001051108818501234</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.570695894770324e-05</v>
+        <v>0.001220176927745342</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0001176623918581754</v>
+        <v>0.000412117806263268</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0002435861097183079</v>
+        <v>0.00351850432343781</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0005748490802943707</v>
+        <v>0.005583555903285742</v>
       </c>
       <c r="CO6" t="n">
-        <v>7.230224582599476e-05</v>
+        <v>0.007201258093118668</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0001813459675759077</v>
+        <v>0.00707935867831111</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0005866249557584524</v>
+        <v>0.003907373175024986</v>
       </c>
       <c r="CR6" t="n">
-        <v>6.792444764869288e-06</v>
+        <v>0.00491752102971077</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0002013605699175969</v>
+        <v>0.006656603422015905</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0003888905339408666</v>
+        <v>0.0006570137338712811</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0006290734745562077</v>
+        <v>0.00121365615632385</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.459966733818874e-05</v>
+        <v>0.000403658312279731</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0003213884774595499</v>
+        <v>0.004584367386996746</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0003538175951689482</v>
+        <v>3.813405055552721e-05</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0003686961717903614</v>
+        <v>0.0001653446815907955</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0001660231209825724</v>
+        <v>0.001194981741718948</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0002565516333561391</v>
+        <v>0.00347998202778399</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0002394986222498119</v>
+        <v>0.001604238408617675</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0002482349518686533</v>
+        <v>0.001186776906251907</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.1307456336217e-05</v>
+        <v>0.0002161642769351602</v>
       </c>
       <c r="DE6" t="n">
-        <v>3.468681097729132e-05</v>
+        <v>0.002183624776080251</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0005467048031277955</v>
+        <v>0.003945149946957827</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.733371704583988e-05</v>
+        <v>0.0007810038514435291</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.896091271191835e-05</v>
+        <v>0.001314433291554451</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0005764492088928819</v>
+        <v>0.002115226350724697</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0003612030413933098</v>
+        <v>0.005151544231921434</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0005482901469804347</v>
+        <v>0.001541801146231592</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0003005493199452758</v>
+        <v>0.007153061684221029</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0004671316419262439</v>
+        <v>0.00385031895712018</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0001831027620937675</v>
+        <v>0.001299460069276392</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001267476473003626</v>
+        <v>0.002741712378337979</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0003652409941423684</v>
+        <v>0.0008921425323933363</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0005733948783017695</v>
+        <v>0.001533281640149653</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0002178933355025947</v>
+        <v>0.001238637254573405</v>
       </c>
       <c r="DS6" t="n">
-        <v>1.394757782691158e-05</v>
+        <v>0.001438577426597476</v>
       </c>
       <c r="DT6" t="n">
-        <v>5.312722350936383e-05</v>
+        <v>0.0003783306747209281</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0001072992599802092</v>
+        <v>0.002551241545006633</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0002309177070856094</v>
+        <v>0.0006213191081769764</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.055462391581386e-05</v>
+        <v>0.0003570008848328143</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.258277916349471e-05</v>
+        <v>0.0009206761606037617</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0004979156074114144</v>
+        <v>0.004317459650337696</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0001764546614140272</v>
+        <v>4.398322198539972e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.000166743848240003</v>
+        <v>0.002531348029151559</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0004672141221817583</v>
+        <v>0.004108735825866461</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001027023317874409</v>
+        <v>0.003069339320063591</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0003711707540787756</v>
+        <v>0.004969408735632896</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0002210829552495852</v>
+        <v>0.007636523805558681</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0002310081908944994</v>
+        <v>0.001128635602071881</v>
       </c>
       <c r="EG6" t="n">
-        <v>2.559293352533132e-05</v>
+        <v>0.0009922685567289591</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0002052127238130197</v>
+        <v>0.003260247875005007</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0002985514292959124</v>
+        <v>2.747296821326017e-05</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0001936733024194837</v>
+        <v>0.0004088013083674014</v>
       </c>
       <c r="EK6" t="n">
-        <v>5.515493103303015e-05</v>
+        <v>0.001324520679190755</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0005732674617320299</v>
+        <v>0.0006683128885924816</v>
       </c>
       <c r="EM6" t="n">
-        <v>4.952503877575509e-05</v>
+        <v>3.640432259999216e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0001152846089098603</v>
+        <v>0.001351002953015268</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0001955691259354353</v>
+        <v>0.0009400960407219827</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0003114739956799895</v>
+        <v>0.004708664957433939</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0002187935606343672</v>
+        <v>0.0001863042125478387</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0003128906537313014</v>
+        <v>0.001216133590787649</v>
       </c>
       <c r="ES6" t="n">
-        <v>6.129065877757967e-05</v>
+        <v>0.004493324086070061</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0005453614867292345</v>
+        <v>0.004580988548696041</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0004358316364232451</v>
+        <v>0.0005082390271127224</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0003754481149371713</v>
+        <v>0.001685042516328394</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0001651203056098893</v>
+        <v>0.00341492984443903</v>
       </c>
       <c r="EX6" t="n">
-        <v>3.636645487858914e-05</v>
+        <v>0.0001026794489007443</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0003338862734381109</v>
+        <v>0.005530718248337507</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0002476769732311368</v>
+        <v>8.738978067412972e-05</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0003032478562090546</v>
+        <v>0.0004070054274052382</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.00025808738428168</v>
+        <v>0.0004300613654777408</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0002784511598292738</v>
+        <v>0.002788248937577009</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0003115687577519566</v>
+        <v>0.0006304529961198568</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0001394061837345362</v>
+        <v>0.0008476726943627</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.0001519034412922338</v>
+        <v>0.0009157347376458347</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.000223872295464389</v>
+        <v>0.001255459734238684</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0003694984770845622</v>
+        <v>0.003290083957836032</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0003153825819026679</v>
+        <v>0.003029424464330077</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0004523724201135337</v>
+        <v>0.0002892117481678724</v>
       </c>
       <c r="FK6" t="n">
-        <v>9.496771963313222e-05</v>
+        <v>0.002237216103821993</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0002413955517113209</v>
+        <v>0.000892159529030323</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0001408437092322856</v>
+        <v>5.559646524488926e-05</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0002914867945946753</v>
+        <v>0.003938975278288126</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0005077803507447243</v>
+        <v>0.009034722112119198</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0001683361042523757</v>
+        <v>0.002810732927173376</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.000192208171938546</v>
+        <v>0.00449086120352149</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0001831417321227491</v>
+        <v>0.004872019402682781</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0005265784566290677</v>
+        <v>0.002326532499864697</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0003693524631671607</v>
+        <v>0.01037964783608913</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.000944059866014868</v>
+        <v>0.004260022193193436</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0002149786159861833</v>
+        <v>0.003523586550727487</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0004996191128157079</v>
+        <v>0.007723339833319187</v>
       </c>
       <c r="FX6" t="n">
-        <v>5.06140204379335e-05</v>
+        <v>0.0001608224993105978</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0002532447397243232</v>
+        <v>0.001635266933590174</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0003019542782567441</v>
+        <v>0.0006473090033978224</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0004278480191715062</v>
+        <v>0.004181938245892525</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0002123992308042943</v>
+        <v>0.001253884402103722</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0001711417135084048</v>
+        <v>0.003680058754980564</v>
       </c>
       <c r="GD6" t="n">
-        <v>5.152818630449474e-05</v>
+        <v>0.00633795652538538</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0003667504934128374</v>
+        <v>0.0003089540987275541</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0004134703194722533</v>
+        <v>0.002261945279315114</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0003912736137863249</v>
+        <v>0.003267842344939709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.004676879849284887</v>
+        <v>0.001823314931243658</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0632065013051033</v>
+        <v>0.01689976267516613</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007693402003496885</v>
+        <v>0.004098369274288416</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02661138959228992</v>
+        <v>0.005175418220460415</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005920668132603168</v>
+        <v>0.00616938853636384</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01363929267972708</v>
+        <v>0.006393714342266321</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001824340783059597</v>
+        <v>0.002666832180693746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002740276278927922</v>
+        <v>0.00086505978833884</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003913332242518663</v>
+        <v>0.001730036223307252</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008990667760372162</v>
+        <v>0.0007302001467905939</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04708258807659149</v>
+        <v>0.02055724337697029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000197465211385861</v>
+        <v>0.004724750760942698</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02541756816208363</v>
+        <v>0.009122647345066071</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00983918271958828</v>
+        <v>0.009638377465307713</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0107008283957839</v>
+        <v>0.002715703565627337</v>
       </c>
       <c r="P7" t="n">
-        <v>0.000918146688491106</v>
+        <v>0.0007996122585609555</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003844799939543009</v>
+        <v>0.004794780630618334</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007448895368725061</v>
+        <v>0.00179680495057255</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001929353922605515</v>
+        <v>0.0004952963208779693</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007864914834499359</v>
+        <v>0.0005348880658857524</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001861663535237312</v>
+        <v>0.0002887091250158846</v>
       </c>
       <c r="V7" t="n">
-        <v>0.005859401077032089</v>
+        <v>0.001607172773219645</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006962759420275688</v>
+        <v>0.001810769783332944</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008195423521101475</v>
+        <v>0.002745426725596189</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003228398505598307</v>
+        <v>0.002745742443948984</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00275943917222321</v>
+        <v>0.0001479166239732876</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00503175426274538</v>
+        <v>0.001967913005501032</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001479440368711948</v>
+        <v>0.0007696719840168953</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.008865604177117348</v>
+        <v>0.003358847694471478</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001352104940451682</v>
+        <v>0.001542903715744615</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001803932711482048</v>
+        <v>0.003730738768354058</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.002673776121810079</v>
+        <v>0.00124771473929286</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.003487406298518181</v>
+        <v>0.004604404326528311</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.002989210886880755</v>
+        <v>0.0001365256030112505</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.002669925801455975</v>
+        <v>0.002803594339638948</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002556013409048319</v>
+        <v>8.945286390371621e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003261894918978214</v>
+        <v>0.0002460453251842409</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.006785473320633173</v>
+        <v>0.005259198602288961</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001597344991751015</v>
+        <v>0.001046133460476995</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002455791691318154</v>
+        <v>0.002097184536978602</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.004020069725811481</v>
+        <v>0.002867190632969141</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.008952880278229713</v>
+        <v>0.002334509044885635</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0001894510933198035</v>
+        <v>0.0009952553082257509</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.004574586637318134</v>
+        <v>0.0009059713920578361</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.004259679466485977</v>
+        <v>8.400756632909179e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.002093054354190826</v>
+        <v>5.233945557847619e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0352950319647789</v>
+        <v>0.01772521063685417</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.003246586071327329</v>
+        <v>0.0002880300162360072</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.004637250676751137</v>
+        <v>0.001174017088487744</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.003224065992981195</v>
+        <v>0.005301442928612232</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.006209144368767738</v>
+        <v>0.003230547299608588</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0007518563652411103</v>
+        <v>0.000736737041734159</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.003849164582788944</v>
+        <v>0.00230766087770462</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.004136314149945974</v>
+        <v>0.001020772149786353</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.002596406731754541</v>
+        <v>0.000103997444966808</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01191825047135353</v>
+        <v>0.002696093404665589</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.008483314886689186</v>
+        <v>0.003826668485999107</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.007060142233967781</v>
+        <v>0.0008074272773228586</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01685231178998947</v>
+        <v>0.0002520426642149687</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.003415205515921116</v>
+        <v>0.00188514415640384</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00763542577624321</v>
+        <v>0.0009128869278356433</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005523978732526302</v>
+        <v>0.000386162253562361</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.003330386476591229</v>
+        <v>0.001404645852744579</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.002101629273965955</v>
+        <v>0.0004916625912301242</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.00245221983641386</v>
+        <v>0.001562294899486005</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003273896872997284</v>
+        <v>0.0003582751378417015</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.002665526466444135</v>
+        <v>0.001339226379059255</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.003074945649132133</v>
+        <v>0.004281280096620321</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.004847696051001549</v>
+        <v>0.001984505448490381</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.005357209593057632</v>
+        <v>0.002289070282131433</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0007849142421036959</v>
+        <v>0.0004187557497061789</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.003919238690286875</v>
+        <v>0.00046125243534334</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003052007406949997</v>
+        <v>0.0009840573184192181</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01909718103706837</v>
+        <v>0.01052817143499851</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.004587883129715919</v>
+        <v>0.0005302864592522383</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.005622787866741419</v>
+        <v>0.003829665016382933</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003099950845353305</v>
+        <v>0.001384276663884521</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.006161611527204514</v>
+        <v>0.002435472561046481</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0004556957865133882</v>
+        <v>0.002647752873599529</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.00179066916462034</v>
+        <v>0.0008596490952186286</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.004455645103007555</v>
+        <v>0.001644611358642578</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.001219990313984454</v>
+        <v>0.000732287997379899</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0108889127150178</v>
+        <v>0.006346838548779488</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.003261613892391324</v>
+        <v>0.0008983011939562857</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.003507489571347833</v>
+        <v>0.00182251341175288</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.003484040033072233</v>
+        <v>0.001394676975905895</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.002293928526341915</v>
+        <v>0.001445397618226707</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.003636182751506567</v>
+        <v>0.0003333678178023547</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0009598432807251811</v>
+        <v>0.0001706852199276909</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.001439340179786086</v>
+        <v>0.0007153344922699034</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.007258256897330284</v>
+        <v>0.002622326835989952</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0004021673812530935</v>
+        <v>0.01047438010573387</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.002285030670464039</v>
+        <v>0.003105741692706943</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.004506899975240231</v>
+        <v>0.00320144509896636</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.007141952402889729</v>
+        <v>0.001486574183218181</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.009273610077798367</v>
+        <v>0.000658111646771431</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.003801882034167647</v>
+        <v>0.001364251598715782</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.004723203368484974</v>
+        <v>0.0006257945206016302</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001909706392325461</v>
+        <v>0.0004463755176402628</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.00101744884159416</v>
+        <v>3.050960367545485e-05</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01047760434448719</v>
+        <v>0.006088363938033581</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.003937339875847101</v>
+        <v>0.001101717352867126</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.004818746820092201</v>
+        <v>0.002479760209098458</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003570682369172573</v>
+        <v>0.001374768209643662</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.003313098335638642</v>
+        <v>0.001418440835550427</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.003535362426191568</v>
+        <v>0.0007080293726176023</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001582208671607077</v>
+        <v>0.0001373856066493317</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0003561903722584248</v>
+        <v>0.00121376384049654</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.005891067441552877</v>
+        <v>0.001389026409015059</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01607639715075493</v>
+        <v>0.00187612057197839</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.00649682991206646</v>
+        <v>0.001499942038208246</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01351922936737537</v>
+        <v>0.0017188536003232</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.00159292749594897</v>
+        <v>0.001028225990012288</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001627626363188028</v>
+        <v>0.004513872787356377</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.002924995962530375</v>
+        <v>0.001161041902378201</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.00664944015443325</v>
+        <v>0.006249650381505489</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.00105234410148114</v>
+        <v>0.001604508841410279</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.003947167657315731</v>
+        <v>0.0002782015653792769</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.005694376770406961</v>
+        <v>0.003247252432629466</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0001399429747834802</v>
+        <v>8.353026350960135e-05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.001325033488683403</v>
+        <v>0.0006997187156230211</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.006397195160388947</v>
+        <v>0.001311859930865467</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.002479106886312366</v>
+        <v>0.001869264640845358</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.002051603514701128</v>
+        <v>0.002312764059752226</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0009106856305152178</v>
+        <v>0.001839022384956479</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0005329407285898924</v>
+        <v>0.003692276077345014</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.001324369106441736</v>
+        <v>0.001501673366874456</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00206666742451489</v>
+        <v>0.004453746601939201</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.003969496581703424</v>
+        <v>0.001292490283958614</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.001115650404244661</v>
+        <v>0.0003214409807696939</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.006413428578525782</v>
+        <v>0.004126508720219135</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.004643936641514301</v>
+        <v>0.002540508983656764</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0008745337254367769</v>
+        <v>0.0002148855419363827</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0006449339562095702</v>
+        <v>0.006165358703583479</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.001392765319906175</v>
+        <v>0.004391047637909651</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.002078250516206026</v>
+        <v>0.0006437927950173616</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.005545870400965214</v>
+        <v>0.003559822449460626</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.004475496243685484</v>
+        <v>0.001010593492537737</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.001751615200191736</v>
+        <v>0.002180334879085422</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.001498371129855514</v>
+        <v>0.001251151203177869</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001825494691729546</v>
+        <v>0.00149968545883894</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.003376473439857364</v>
+        <v>0.000738870061468333</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001313287764787674</v>
+        <v>0.0001059296919265762</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0004548575961962342</v>
+        <v>0.001059849513694644</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001874505891464651</v>
+        <v>1.003498618956655e-05</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01044645439833403</v>
+        <v>0.002995803253725171</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001832117675803602</v>
+        <v>0.0003852950176224113</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.005837826058268547</v>
+        <v>0.002191198989748955</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.006748198065906763</v>
+        <v>0.0003809103509411216</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01033670734614134</v>
+        <v>0.001326192170381546</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.006631731521338224</v>
+        <v>0.0008278931491076946</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.003486301517114043</v>
+        <v>0.0004212397907394916</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0003092076512984931</v>
+        <v>0.001901124836876988</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001219054174725898</v>
+        <v>0.0005732718273065984</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01050810888409615</v>
+        <v>0.00699327327311039</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001463828724808991</v>
+        <v>0.0008654664270579815</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.004862574860453606</v>
+        <v>0.00231866305693984</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003952600993216038</v>
+        <v>0.0007559648947790265</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.002898440696299076</v>
+        <v>0.001601405441761017</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.004617250058799982</v>
+        <v>0.0001318839786108583</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.002201383234933019</v>
+        <v>0.0003465947229415178</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.002117384225130081</v>
+        <v>0.001567864557728171</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0003687965800054371</v>
+        <v>0.0002800244837999344</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.002791496925055981</v>
+        <v>0.001706806593574584</v>
       </c>
       <c r="FI7" t="n">
-        <v>6.660709186689928e-05</v>
+        <v>0.00193098047748208</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.004276526160538197</v>
+        <v>0.002326314570382237</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.002001999411731958</v>
+        <v>0.0004693989467341453</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.002420612145215273</v>
+        <v>0.0003060495364479721</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001141052809543908</v>
+        <v>0.0009293865296058357</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001595306443050504</v>
+        <v>0.001288719824515283</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.003355273045599461</v>
+        <v>0.001407967996783555</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.003918735776096582</v>
+        <v>0.001725834445096552</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.003968678414821625</v>
+        <v>0.005016160663217306</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.004885123111307621</v>
+        <v>0.0002260426990687847</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.001181246829219162</v>
+        <v>0.0004665270680561662</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.004154475405812263</v>
+        <v>0.0002273038844577968</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.001479245023801923</v>
+        <v>0.001820966834202409</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.001008672174066305</v>
+        <v>0.0003780827682930976</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.003343112766742706</v>
+        <v>0.0009252622257918119</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.004789459519088268</v>
+        <v>0.002225775038823485</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.003595056012272835</v>
+        <v>0.0009062918834388256</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.004583399742841721</v>
+        <v>0.003747829701751471</v>
       </c>
       <c r="GA7" t="n">
-        <v>7.712165825068951e-06</v>
+        <v>0.0005675579304806888</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0005226210341788828</v>
+        <v>0.001689959899522364</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.01337885390967131</v>
+        <v>0.001647592755034566</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.005115482956171036</v>
+        <v>0.002311119576916099</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.01403980422765017</v>
+        <v>0.003718317020684481</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.002980181016027927</v>
+        <v>0.001076359418220818</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.000604941975325346</v>
+        <v>0.0003384160809218884</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.007168769370764494</v>
+        <v>0.0008582671289332211</v>
       </c>
       <c r="B8" t="n">
-        <v>0.08400869369506836</v>
+        <v>0.01235334668308496</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01514997705817223</v>
+        <v>0.00265890546143055</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03835845738649368</v>
+        <v>0.005583470687270164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01671245135366917</v>
+        <v>0.002556846477091312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02282984182238579</v>
+        <v>0.002579392865300179</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005217849276959896</v>
+        <v>0.002665703650563955</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001589244930073619</v>
+        <v>0.002938581164926291</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01229265332221985</v>
+        <v>0.000947249005548656</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007891359739005566</v>
+        <v>0.000198321882635355</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06923197209835052</v>
+        <v>0.01339288149029016</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006324692629277706</v>
+        <v>0.003007128601893783</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04343052580952644</v>
+        <v>0.008152668364346027</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02282565832138062</v>
+        <v>0.003069047117605805</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02280501648783684</v>
+        <v>0.0003185036184731871</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002433150075376034</v>
+        <v>0.001572821754962206</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01150477677583694</v>
+        <v>0.0005362957599572837</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01991237886250019</v>
+        <v>0.001001521246507764</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002175789326429367</v>
+        <v>0.0008840595255605876</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01646007224917412</v>
+        <v>0.001288469531573355</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004029097966849804</v>
+        <v>0.0005349917919375002</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00686568534001708</v>
+        <v>0.0004054158926010132</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00600510323420167</v>
+        <v>0.0005022325785830617</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01371177937835455</v>
+        <v>0.0008116892422549427</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.008617294020950794</v>
+        <v>0.0001827455998864025</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000619049184024334</v>
+        <v>0.0007815764984115958</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005736030638217926</v>
+        <v>0.00238846312277019</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.008499878458678722</v>
+        <v>0.0003504430060274899</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01216092985123396</v>
+        <v>0.0004335992853157222</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001176318037323654</v>
+        <v>0.0007715797401033342</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001204777276143432</v>
+        <v>0.00161117035895586</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0005975330714136362</v>
+        <v>3.753666533157229e-07</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001263311598449945</v>
+        <v>0.002578616375103593</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.003389801364392042</v>
+        <v>0.0002771464933175594</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001748283393681049</v>
+        <v>0.000101654208265245</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004766212310642004</v>
+        <v>4.023023939225823e-05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.00039886892773211</v>
+        <v>0.0006885769544169307</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01355666294693947</v>
+        <v>0.00369431241415441</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00181340763811022</v>
+        <v>0.0006319080712273717</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001007337588816881</v>
+        <v>0.001781676895916462</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.00396815175190568</v>
+        <v>0.003018844407051802</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.009346594102680683</v>
+        <v>0.001258069765754044</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002216050866991282</v>
+        <v>0.0005662042531184852</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.001768440473824739</v>
+        <v>0.0002216149587184191</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.003349442966282368</v>
+        <v>1.456955214962363e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.01894150488078594</v>
+        <v>0.0009229271672666073</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.05117499828338623</v>
+        <v>0.008814523927867413</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.004235835280269384</v>
+        <v>0.0006431342335417867</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01422409433871508</v>
+        <v>0.002114072907716036</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0006149836117401719</v>
+        <v>0.001310931635089219</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002493135631084442</v>
+        <v>0.0002820744412019849</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.004475251771509647</v>
+        <v>0.0002704568323679268</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004957276396453381</v>
+        <v>0.0007313981186598539</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.289913577958941e-05</v>
+        <v>0.0008038402302190661</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.003900050418451428</v>
+        <v>0.0003047957143280655</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01419290620833635</v>
+        <v>0.001147142145782709</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.01498660817742348</v>
+        <v>0.002438667695969343</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.00987621396780014</v>
+        <v>0.0002036931400652975</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.03041865304112434</v>
+        <v>0.001643642783164978</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0114520862698555</v>
+        <v>0.0009635684546083212</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005769550334662199</v>
+        <v>0.0003855410031974316</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.009007807821035385</v>
+        <v>0.001583516364917159</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.01371551956981421</v>
+        <v>0.0009202237706631422</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.005319294985383749</v>
+        <v>4.030385753139853e-06</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001678012893535197</v>
+        <v>0.0005703308270312846</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.00421602139249444</v>
+        <v>0.0006805190350860357</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001197386300191283</v>
+        <v>0.0006344128050841391</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.002668196801096201</v>
+        <v>0.002335238037630916</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.007391213439404964</v>
+        <v>0.0006977166631259024</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003704114118590951</v>
+        <v>0.0005755909369327128</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004745723679661751</v>
+        <v>0.0003090956888627261</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.00354213360697031</v>
+        <v>0.0008450839086435735</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0123633174225688</v>
+        <v>0.001151933800429106</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.03226429596543312</v>
+        <v>0.006775669753551483</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.008964402601122856</v>
+        <v>0.0002123554877471179</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.01466293819248676</v>
+        <v>0.001830405555665493</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.007255834992974997</v>
+        <v>0.000205130796530284</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.004909671377390623</v>
+        <v>0.000756445515435189</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0013060187920928</v>
+        <v>0.0009055848349817097</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.003628767095506191</v>
+        <v>0.000358565419446677</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.004666110966354609</v>
+        <v>0.001583638950251043</v>
       </c>
       <c r="CD8" t="n">
-        <v>7.24883284419775e-05</v>
+        <v>0.0007187603041529655</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.01429480034857988</v>
+        <v>0.003986473195254803</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003446143120527267</v>
+        <v>0.0008164008613675833</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.005361473653465509</v>
+        <v>0.002052859868854284</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.003208813956007361</v>
+        <v>0.000168026308529079</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.003456777427345514</v>
+        <v>0.0007171215256676078</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003390894504263997</v>
+        <v>0.0001324456825386733</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001868662191554904</v>
+        <v>0.0001747522910591215</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001375643769279122</v>
+        <v>0.0007147130672819912</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.01034243311733007</v>
+        <v>0.000586367619689554</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.005344661418348551</v>
+        <v>0.005389233119785786</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0008646337082609534</v>
+        <v>0.001519326586276293</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.004536115564405918</v>
+        <v>0.002742988057434559</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00704663060605526</v>
+        <v>0.0005250803660601377</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.005221457220613956</v>
+        <v>0.0002233973646070808</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.003766468027606606</v>
+        <v>0.001754098921082914</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.01022507529705763</v>
+        <v>0.0002878872910514474</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.002147860126569867</v>
+        <v>0.000501283910125494</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003004360478371382</v>
+        <v>0.0004019372863695025</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.01262617576867342</v>
+        <v>0.003816339652985334</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.004188364837318659</v>
+        <v>0.0007476104656234384</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.006465325597673655</v>
+        <v>0.00194906210526824</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.001250472385436296</v>
+        <v>0.0002263396745547652</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.006638104561716318</v>
+        <v>0.0007692127837799489</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.003537885379046202</v>
+        <v>0.0001733384851831943</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001353365718387067</v>
+        <v>0.0001654745719861239</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0009615187300369143</v>
+        <v>0.001008256804198027</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.00292835128493607</v>
+        <v>0.000316304707666859</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02382145635783672</v>
+        <v>0.003333717584609985</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.005392674822360277</v>
+        <v>0.002048924332484603</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.02531644143164158</v>
+        <v>0.002140658441931009</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.005150152370333672</v>
+        <v>0.0006816519889980555</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01864339411258698</v>
+        <v>0.002420304110273719</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0004273103550076485</v>
+        <v>0.001075128791853786</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.003845891682431102</v>
+        <v>0.003687205258756876</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.001914603868499398</v>
+        <v>0.0001334428525296971</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.003806686960160732</v>
+        <v>0.0003806505119428039</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.005472778342664242</v>
+        <v>0.001947971992194653</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.006142724305391312</v>
+        <v>0.0007506113033741713</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.001318346243351698</v>
+        <v>0.0004492287407629192</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01607578434050083</v>
+        <v>0.0007839137688279152</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.006666045635938644</v>
+        <v>0.0007177043589763343</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.007697063032537699</v>
+        <v>0.0003081820032093674</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0004038852639496326</v>
+        <v>0.0008865515701472759</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.006299121305346489</v>
+        <v>0.00300292856991291</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001753120799548924</v>
+        <v>0.0003155023150611669</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.00940307043492794</v>
+        <v>0.001079326262697577</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.008727769367396832</v>
+        <v>0.0005356250330805779</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0109854806214571</v>
+        <v>0.001093649887479842</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.008455118164420128</v>
+        <v>0.0008421199163421988</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.008394621312618256</v>
+        <v>0.002823579125106335</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0005422791000455618</v>
+        <v>0.0003037920687347651</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.005415942054241896</v>
+        <v>0.003540116129443049</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.008885478600859642</v>
+        <v>0.002459415467455983</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0009667454869486392</v>
+        <v>0.0001553444308228791</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.00673741614446044</v>
+        <v>0.003444020170718431</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.004196364898234606</v>
+        <v>0.0006169325206428766</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.004941251128911972</v>
+        <v>0.002049729693681002</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.005822556558996439</v>
+        <v>0.0005458498490042984</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01200977806001902</v>
+        <v>0.001032212632708251</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.002387115731835365</v>
+        <v>0.0003015967376995832</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.002615044824779034</v>
+        <v>0.0005637189606204629</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001126967486925423</v>
+        <v>0.0004039207706227899</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.002820771420374513</v>
+        <v>0.0001754186523612589</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.006307987496256828</v>
+        <v>0.003014714922755957</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.00712327565997839</v>
+        <v>0.000230419565923512</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.002478004200384021</v>
+        <v>0.001601724768988788</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.003606909886002541</v>
+        <v>0.001112741185352206</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01243461389094591</v>
+        <v>0.001123985275626183</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.002290689619258046</v>
+        <v>0.0008683926425874233</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0047786352224648</v>
+        <v>0.0008662859909236431</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.001136377453804016</v>
+        <v>0.001322263502515852</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.001670385361649096</v>
+        <v>0.0007902740035206079</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.01336706522852182</v>
+        <v>0.004499406553804874</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001094749895855784</v>
+        <v>0.0006828730693086982</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00825103372335434</v>
+        <v>0.002227142220363021</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.002256658626720309</v>
+        <v>8.594711835030466e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.006631257012486458</v>
+        <v>0.0008933839853852987</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.003920706454664469</v>
+        <v>5.022838013246655e-05</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.002112931804731488</v>
+        <v>0.0004770864616148174</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0008997987606562674</v>
+        <v>0.001111400779336691</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0004424115759320557</v>
+        <v>0.001105121104046702</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.006782719399780035</v>
+        <v>0.001504173735156655</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.002183118602260947</v>
+        <v>0.001669439719989896</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.003272326430305839</v>
+        <v>0.0008279662579298019</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.002600597916170955</v>
+        <v>0.0002955266390927136</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.006029484327882528</v>
+        <v>0.0006223982782103121</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.002688414882868528</v>
+        <v>0.0004810647806152701</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.002219535876065493</v>
+        <v>0.001018163049593568</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.002664494328200817</v>
+        <v>0.002677629701793194</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.01555230654776096</v>
+        <v>0.0005405893898569047</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.02489249780774117</v>
+        <v>0.003286691149696708</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.00623836787417531</v>
+        <v>0.0004165172576904297</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.03338128700852394</v>
+        <v>0.0005992406513541937</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001923635601997375</v>
+        <v>0.0005992708611302078</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.003685546340420842</v>
+        <v>0.0007832094561308622</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.003319485578685999</v>
+        <v>0.0009473758982494473</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.003855146002024412</v>
+        <v>0.0004905120586045086</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.001607406651601195</v>
+        <v>0.002036656253039837</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.01070744916796684</v>
+        <v>0.002018321771174669</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.00641935970634222</v>
+        <v>0.003558801952749491</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.002937021898105741</v>
+        <v>2.197374124079943e-05</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.002430598717182875</v>
+        <v>0.001003868877887726</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.01323564257472754</v>
+        <v>0.004214874934405088</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.005114351399242878</v>
+        <v>0.00118178129196167</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01468470133841038</v>
+        <v>0.00146994786337018</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.001472985721193254</v>
+        <v>0.001541491714306176</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.002848708536475897</v>
+        <v>5.608268838841468e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5551,1140 +5551,1140 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.362468876526691e-05</v>
+        <v>0.06307490170001984</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0006537125445902348</v>
+        <v>0.1053879037499428</v>
       </c>
       <c r="C10" t="n">
-        <v>8.722946222405881e-05</v>
+        <v>0.0001103747636079788</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002359287609579042</v>
+        <v>0.018001364544034</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002788411220535636</v>
+        <v>0.0159799549728632</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0003073039988521487</v>
+        <v>0.09357412904500961</v>
       </c>
       <c r="G10" t="n">
-        <v>2.786457480397075e-05</v>
+        <v>0.02364145033061504</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001144204434240237</v>
+        <v>0.02935198880732059</v>
       </c>
       <c r="I10" t="n">
-        <v>8.789294224698097e-05</v>
+        <v>0.03237006813287735</v>
       </c>
       <c r="J10" t="n">
-        <v>6.37409721093718e-06</v>
+        <v>0.06228522583842278</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0006373744690790772</v>
+        <v>0.1334042251110077</v>
       </c>
       <c r="L10" t="n">
-        <v>8.636270649731159e-05</v>
+        <v>0.004771580919623375</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0003034668625332415</v>
+        <v>0.03262372314929962</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0002640743623487651</v>
+        <v>0.02415797300636768</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0003983533242717385</v>
+        <v>0.08962063491344452</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0001803771738195792</v>
+        <v>0.01397794857621193</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.736921881791204e-05</v>
+        <v>0.000335419550538063</v>
       </c>
       <c r="R10" t="n">
-        <v>0.000146789345308207</v>
+        <v>0.05468524992465973</v>
       </c>
       <c r="S10" t="n">
-        <v>6.429673521779478e-05</v>
+        <v>0.0009317579679191113</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0001259085111087188</v>
+        <v>0.01055426057428122</v>
       </c>
       <c r="U10" t="n">
-        <v>8.845623597153462e-06</v>
+        <v>0.01929241418838501</v>
       </c>
       <c r="V10" t="n">
-        <v>4.022431312478147e-06</v>
+        <v>0.03678923845291138</v>
       </c>
       <c r="W10" t="n">
-        <v>5.871621033293195e-05</v>
+        <v>0.01984278112649918</v>
       </c>
       <c r="X10" t="n">
-        <v>9.033869719132781e-05</v>
+        <v>0.01068090368062258</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.411536231898936e-06</v>
+        <v>0.00328541686758399</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.91110586153809e-06</v>
+        <v>0.03309393674135208</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.072740532341413e-05</v>
+        <v>0.008549170568585396</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.199033279903233e-05</v>
+        <v>0.01564698666334152</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0001047152181854472</v>
+        <v>0.0161642674356699</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001735396945150569</v>
+        <v>0.01534230448305607</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001190644688904285</v>
+        <v>0.04688596725463867</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0001360938767902553</v>
+        <v>0.04754539579153061</v>
       </c>
       <c r="AG10" t="n">
-        <v>8.261276889243163e-06</v>
+        <v>0.006600494962185621</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.77818204369396e-05</v>
+        <v>0.01640097983181477</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.02306130429497e-05</v>
+        <v>0.05260058119893074</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0001372069382341579</v>
+        <v>0.003824735060334206</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.640679304022342e-05</v>
+        <v>0.01803840138018131</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0001971861638594419</v>
+        <v>0.02408980391919613</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.18508900818415e-05</v>
+        <v>0.01785704120993614</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.540279481559992e-05</v>
+        <v>0.0317704938352108</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.488319584401324e-05</v>
+        <v>0.005587341263890266</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.771209569298662e-05</v>
+        <v>0.0132073275744915</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.038609065697528e-05</v>
+        <v>0.01938627474009991</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.504642932559364e-05</v>
+        <v>0.03750232979655266</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.68186888913624e-05</v>
+        <v>0.02446402609348297</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0001014204608509317</v>
+        <v>0.04773956909775734</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0004861050983890891</v>
+        <v>0.08856316655874252</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.804072472732514e-05</v>
+        <v>0.00953780859708786</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0001184393840958364</v>
+        <v>0.01087414752691984</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.589984645368531e-06</v>
+        <v>0.03113785199820995</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.274745929753408e-05</v>
+        <v>0.04072375223040581</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001850129920057952</v>
+        <v>0.00817326083779335</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0001084419200196862</v>
+        <v>0.004144230857491493</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.910713975434192e-06</v>
+        <v>0.01869891956448555</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.852051354944706e-05</v>
+        <v>0.00135636399500072</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0001180186591227539</v>
+        <v>0.01833335123956203</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.362040145788342e-05</v>
+        <v>0.009374816901981831</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.557745235913899e-06</v>
+        <v>0.03370632976293564</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0002663775521796197</v>
+        <v>0.003951582126319408</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0002207486977567896</v>
+        <v>0.04400931298732758</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.000103194142866414</v>
+        <v>0.0005564233288168907</v>
       </c>
       <c r="BJ10" t="n">
-        <v>3.195261342625599e-06</v>
+        <v>0.01264019124209881</v>
       </c>
       <c r="BK10" t="n">
-        <v>8.796567999524996e-05</v>
+        <v>0.03164147213101387</v>
       </c>
       <c r="BL10" t="n">
-        <v>7.386918150587007e-05</v>
+        <v>0.005332041531801224</v>
       </c>
       <c r="BM10" t="n">
-        <v>7.900067430455238e-05</v>
+        <v>0.004122283775359392</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.915813431376591e-05</v>
+        <v>0.001248790882527828</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.871198663953692e-05</v>
+        <v>0.00269313994795084</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.955306940246373e-05</v>
+        <v>0.01021428685635328</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.485261549940333e-05</v>
+        <v>1.668231561779976e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>8.221218013204634e-05</v>
+        <v>0.05526763945817947</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.666329055500682e-05</v>
+        <v>0.006549232173711061</v>
       </c>
       <c r="BT10" t="n">
-        <v>2.16309999814257e-05</v>
+        <v>0.02799361757934093</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.354770787060261e-05</v>
+        <v>0.01659994199872017</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0002782572410069406</v>
+        <v>0.05802822858095169</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.19569982518442e-05</v>
+        <v>0.01160531118512154</v>
       </c>
       <c r="BX10" t="n">
-        <v>9.901632438413799e-05</v>
+        <v>0.03076763451099396</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.278272172086872e-05</v>
+        <v>0.006146412342786789</v>
       </c>
       <c r="BZ10" t="n">
-        <v>7.365398050751537e-05</v>
+        <v>0.03958381712436676</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001139395753853023</v>
+        <v>0.01171463448554277</v>
       </c>
       <c r="CB10" t="n">
-        <v>2.314010998816229e-06</v>
+        <v>0.001080519519746304</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.537656786851585e-05</v>
+        <v>0.01701092533767223</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.605629586265422e-05</v>
+        <v>0.01473087817430496</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0001120239321608096</v>
+        <v>0.03184303641319275</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.164314736319284e-07</v>
+        <v>0.005504399072378874</v>
       </c>
       <c r="CG10" t="n">
-        <v>5.518261968973093e-05</v>
+        <v>0.008494991809129715</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.05938606793643e-05</v>
+        <v>0.01231368631124496</v>
       </c>
       <c r="CI10" t="n">
-        <v>3.746717993635684e-05</v>
+        <v>0.0285104364156723</v>
       </c>
       <c r="CJ10" t="n">
-        <v>7.203793211374432e-05</v>
+        <v>0.01884897612035275</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.311057530983817e-05</v>
+        <v>0.009262679144740105</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.203071042255033e-05</v>
+        <v>0.006949326954782009</v>
       </c>
       <c r="CM10" t="n">
-        <v>5.575796240009367e-05</v>
+        <v>0.001161688938736916</v>
       </c>
       <c r="CN10" t="n">
-        <v>9.023317397804931e-05</v>
+        <v>0.05139520019292831</v>
       </c>
       <c r="CO10" t="n">
-        <v>2.602700078568887e-05</v>
+        <v>0.008814770728349686</v>
       </c>
       <c r="CP10" t="n">
-        <v>3.172046854160726e-05</v>
+        <v>0.02370203100144863</v>
       </c>
       <c r="CQ10" t="n">
-        <v>7.545807602582499e-05</v>
+        <v>0.0005722800269722939</v>
       </c>
       <c r="CR10" t="n">
-        <v>8.054803765844554e-05</v>
+        <v>0.04160137474536896</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0001558643707539886</v>
+        <v>0.01531132869422436</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0001887972321128473</v>
+        <v>3.543682396411896e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>5.527815665118396e-05</v>
+        <v>0.00701916916295886</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.431997225154191e-05</v>
+        <v>0.01031465642154217</v>
       </c>
       <c r="CW10" t="n">
-        <v>9.672377200331539e-05</v>
+        <v>0.02956297807395458</v>
       </c>
       <c r="CX10" t="n">
-        <v>2.18420427700039e-05</v>
+        <v>0.006657399702817202</v>
       </c>
       <c r="CY10" t="n">
-        <v>5.527075700229034e-05</v>
+        <v>0.007987054064869881</v>
       </c>
       <c r="CZ10" t="n">
-        <v>9.981727998820134e-06</v>
+        <v>0.01109167747199535</v>
       </c>
       <c r="DA10" t="n">
-        <v>5.772678559878841e-05</v>
+        <v>0.02744703739881516</v>
       </c>
       <c r="DB10" t="n">
-        <v>5.134956518304534e-05</v>
+        <v>0.01176572218537331</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.989937845792156e-05</v>
+        <v>0.01369572058320045</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.534254352009157e-06</v>
+        <v>0.009156067855656147</v>
       </c>
       <c r="DE10" t="n">
-        <v>5.878490628674626e-05</v>
+        <v>0.009439547546207905</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0001443789078621194</v>
+        <v>0.01741647720336914</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0001564725098432973</v>
+        <v>0.0223887711763382</v>
       </c>
       <c r="DH10" t="n">
-        <v>3.993441350758076e-05</v>
+        <v>0.01228660717606544</v>
       </c>
       <c r="DI10" t="n">
-        <v>6.198462506290525e-05</v>
+        <v>0.05382538586854935</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0001363044138997793</v>
+        <v>0.03036850318312645</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0001083280803868547</v>
+        <v>0.0009559206664562225</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0001012512220768258</v>
+        <v>0.004717485513538122</v>
       </c>
       <c r="DM10" t="n">
-        <v>7.787383219692856e-05</v>
+        <v>0.02829151973128319</v>
       </c>
       <c r="DN10" t="n">
-        <v>9.293053153669462e-06</v>
+        <v>0.00981089286506176</v>
       </c>
       <c r="DO10" t="n">
-        <v>6.236802437342703e-05</v>
+        <v>0.01958531513810158</v>
       </c>
       <c r="DP10" t="n">
-        <v>5.293543654261157e-05</v>
+        <v>0.01261733844876289</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0002134438836947083</v>
+        <v>0.01345005072653294</v>
       </c>
       <c r="DR10" t="n">
-        <v>2.80618951364886e-05</v>
+        <v>0.005381821189075708</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0001191929040942341</v>
+        <v>0.03150089830160141</v>
       </c>
       <c r="DT10" t="n">
-        <v>3.163125438732095e-05</v>
+        <v>0.00733553571626544</v>
       </c>
       <c r="DU10" t="n">
-        <v>8.26949835754931e-05</v>
+        <v>0.0251365602016449</v>
       </c>
       <c r="DV10" t="n">
-        <v>4.753796383738518e-05</v>
+        <v>0.006510206498205662</v>
       </c>
       <c r="DW10" t="n">
-        <v>5.096373570268042e-05</v>
+        <v>0.01829385384917259</v>
       </c>
       <c r="DX10" t="n">
-        <v>2.106113242916763e-05</v>
+        <v>0.003920881077647209</v>
       </c>
       <c r="DY10" t="n">
-        <v>3.477793143247254e-05</v>
+        <v>0.001328612677752972</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0001369327655993402</v>
+        <v>0.02064661495387554</v>
       </c>
       <c r="EA10" t="n">
-        <v>1.004597015707986e-05</v>
+        <v>0.02923509478569031</v>
       </c>
       <c r="EB10" t="n">
-        <v>8.58979910844937e-05</v>
+        <v>0.03799204900860786</v>
       </c>
       <c r="EC10" t="n">
-        <v>8.501535194227472e-05</v>
+        <v>0.008334105834364891</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0001820118486648425</v>
+        <v>0.0153736537322402</v>
       </c>
       <c r="EE10" t="n">
-        <v>3.23367421515286e-05</v>
+        <v>0.01655968278646469</v>
       </c>
       <c r="EF10" t="n">
-        <v>4.678710683947429e-05</v>
+        <v>0.01377271488308907</v>
       </c>
       <c r="EG10" t="n">
-        <v>9.790588228497654e-05</v>
+        <v>0.002333429176360369</v>
       </c>
       <c r="EH10" t="n">
-        <v>2.633419853736996e-06</v>
+        <v>0.01662077382206917</v>
       </c>
       <c r="EI10" t="n">
-        <v>6.741705874446779e-05</v>
+        <v>0.02445342019200325</v>
       </c>
       <c r="EJ10" t="n">
-        <v>4.505593824433163e-05</v>
+        <v>0.01785639114677906</v>
       </c>
       <c r="EK10" t="n">
-        <v>5.24223069078289e-05</v>
+        <v>0.01130727306008339</v>
       </c>
       <c r="EL10" t="n">
-        <v>9.603885700926185e-05</v>
+        <v>0.008211761713027954</v>
       </c>
       <c r="EM10" t="n">
-        <v>1.564013018651167e-06</v>
+        <v>0.0002842266112565994</v>
       </c>
       <c r="EN10" t="n">
-        <v>2.475193468853831e-05</v>
+        <v>0.007830213755369186</v>
       </c>
       <c r="EO10" t="n">
-        <v>2.073068026220426e-05</v>
+        <v>0.01119418255984783</v>
       </c>
       <c r="EP10" t="n">
-        <v>5.423601760412566e-05</v>
+        <v>0.01099726650863886</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0001031678184517659</v>
+        <v>0.003518219571560621</v>
       </c>
       <c r="ER10" t="n">
-        <v>3.484855551505461e-05</v>
+        <v>0.01323778461664915</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0001287634368054569</v>
+        <v>0.01851066760718822</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0001273887028219178</v>
+        <v>0.0335456021130085</v>
       </c>
       <c r="EU10" t="n">
-        <v>8.25670940685086e-06</v>
+        <v>0.0101389791816473</v>
       </c>
       <c r="EV10" t="n">
-        <v>5.56548111489974e-05</v>
+        <v>0.0006730940076522529</v>
       </c>
       <c r="EW10" t="n">
-        <v>2.663740451680496e-05</v>
+        <v>0.02576389536261559</v>
       </c>
       <c r="EX10" t="n">
-        <v>7.652402928215452e-06</v>
+        <v>0.01395296771079302</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0001054444728652015</v>
+        <v>0.03602157533168793</v>
       </c>
       <c r="EZ10" t="n">
-        <v>7.092974101396976e-06</v>
+        <v>0.003860858269035816</v>
       </c>
       <c r="FA10" t="n">
-        <v>5.404465991887264e-05</v>
+        <v>0.006344940513372421</v>
       </c>
       <c r="FB10" t="n">
-        <v>2.371140908508096e-05</v>
+        <v>0.01698688417673111</v>
       </c>
       <c r="FC10" t="n">
-        <v>4.830291800317355e-05</v>
+        <v>0.0247784536331892</v>
       </c>
       <c r="FD10" t="n">
-        <v>5.999162385705858e-05</v>
+        <v>0.01471265219151974</v>
       </c>
       <c r="FE10" t="n">
-        <v>2.082526407320984e-06</v>
+        <v>0.01218229252845049</v>
       </c>
       <c r="FF10" t="n">
-        <v>2.412499270576518e-06</v>
+        <v>0.00153442076407373</v>
       </c>
       <c r="FG10" t="n">
-        <v>2.995231989189051e-05</v>
+        <v>0.002347149886190891</v>
       </c>
       <c r="FH10" t="n">
-        <v>2.80014664895134e-05</v>
+        <v>0.04391274973750114</v>
       </c>
       <c r="FI10" t="n">
-        <v>6.715128984069452e-05</v>
+        <v>0.01697685196995735</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0001382529444526881</v>
+        <v>0.005280526354908943</v>
       </c>
       <c r="FK10" t="n">
-        <v>5.884820711798966e-05</v>
+        <v>0.003448084928095341</v>
       </c>
       <c r="FL10" t="n">
-        <v>8.315445302287117e-05</v>
+        <v>0.03439919278025627</v>
       </c>
       <c r="FM10" t="n">
-        <v>6.89022199367173e-05</v>
+        <v>0.01610036008059978</v>
       </c>
       <c r="FN10" t="n">
-        <v>7.094733155099675e-05</v>
+        <v>0.03843779861927032</v>
       </c>
       <c r="FO10" t="n">
-        <v>4.790259845321998e-05</v>
+        <v>0.007727329153567553</v>
       </c>
       <c r="FP10" t="n">
-        <v>6.21903600404039e-05</v>
+        <v>0.02610764652490616</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0002702029305510223</v>
+        <v>0.01745426654815674</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.33621574100107e-05</v>
+        <v>0.05730548501014709</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0001397436572005972</v>
+        <v>0.038863155990839</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0001844321086537093</v>
+        <v>0.009997231885790825</v>
       </c>
       <c r="FU10" t="n">
-        <v>5.052139385952614e-05</v>
+        <v>0.01687032356858253</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0001997930958168581</v>
+        <v>0.002722668927162886</v>
       </c>
       <c r="FW10" t="n">
-        <v>2.893502369261114e-06</v>
+        <v>0.0004065632820129395</v>
       </c>
       <c r="FX10" t="n">
-        <v>8.330723358085379e-05</v>
+        <v>0.02607262693345547</v>
       </c>
       <c r="FY10" t="n">
-        <v>5.661652539856732e-05</v>
+        <v>0.02111527509987354</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0001082293456420302</v>
+        <v>0.01510810106992722</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0001427535753464326</v>
+        <v>0.00962141714990139</v>
       </c>
       <c r="GB10" t="n">
-        <v>6.071677489671856e-07</v>
+        <v>0.02495861053466797</v>
       </c>
       <c r="GC10" t="n">
-        <v>1.178123784484342e-05</v>
+        <v>0.03158798441290855</v>
       </c>
       <c r="GD10" t="n">
-        <v>2.229841084044892e-05</v>
+        <v>0.02726544067263603</v>
       </c>
       <c r="GE10" t="n">
-        <v>6.958498124731705e-05</v>
+        <v>0.006975656375288963</v>
       </c>
       <c r="GF10" t="n">
-        <v>3.918195216101594e-05</v>
+        <v>0.02581400237977505</v>
       </c>
       <c r="GG10" t="n">
-        <v>1.572974724695086e-05</v>
+        <v>0.033157117664814</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0001283310120925307</v>
+        <v>3.850834762175737e-09</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001384068047627807</v>
+        <v>3.654250235740619e-09</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0002000303938984871</v>
+        <v>2.572130286537799e-10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0006055764970369637</v>
+        <v>5.563526528362672e-09</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001120878150686622</v>
+        <v>2.679573896102738e-09</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0004562905814964324</v>
+        <v>6.391841722575009e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0001716330734780058</v>
+        <v>8.016570740565498e-11</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0002372929448029026</v>
+        <v>8.718470390078892e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001110057710320689</v>
+        <v>2.315754255022284e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0002909993345383555</v>
+        <v>5.014921811152817e-09</v>
       </c>
       <c r="K11" t="n">
-        <v>0.001182552194222808</v>
+        <v>2.743635763025054e-09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002616197452880442</v>
+        <v>1.363830492984164e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0004238318069837987</v>
+        <v>5.171874928322495e-09</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0008232941036112607</v>
+        <v>2.185204683868847e-09</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0004770507221110165</v>
+        <v>7.562224624280134e-09</v>
       </c>
       <c r="P11" t="n">
-        <v>8.908077143132687e-05</v>
+        <v>1.090519896607134e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.992141086608171e-05</v>
+        <v>1.299902963047828e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001345522759947926</v>
+        <v>2.352862793486565e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>4.207906022202224e-05</v>
+        <v>8.942857565585882e-10</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0003502019389998168</v>
+        <v>1.852620279407802e-10</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0001682625006651506</v>
+        <v>3.698051309619643e-10</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0001643310824874789</v>
+        <v>6.431878363244437e-10</v>
       </c>
       <c r="W11" t="n">
-        <v>7.06999417161569e-05</v>
+        <v>1.098262703003172e-09</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0002673647541087121</v>
+        <v>1.605754307298923e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.903199442196637e-05</v>
+        <v>7.049657524405006e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0001281514560105279</v>
+        <v>1.209014333092284e-09</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.969636499183252e-05</v>
+        <v>2.984708313835682e-11</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.243962808279321e-05</v>
+        <v>1.911037994517528e-09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0001689051714492962</v>
+        <v>1.90515359044241e-09</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0002712284913286567</v>
+        <v>1.407173710887832e-09</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.623828939045779e-05</v>
+        <v>1.713230390887333e-10</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0001081108348444104</v>
+        <v>1.316650122262786e-09</v>
       </c>
       <c r="AG11" t="n">
-        <v>9.821826097322628e-06</v>
+        <v>1.53234103184019e-09</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0002210704260505736</v>
+        <v>1.018795270368855e-09</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0001448656403226778</v>
+        <v>2.545612387550023e-09</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0001216519813169725</v>
+        <v>4.55951248978792e-11</v>
       </c>
       <c r="AK11" t="n">
-        <v>5.760229396400973e-05</v>
+        <v>3.914555346540283e-10</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0004499848000705242</v>
+        <v>2.371564056247166e-11</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0001905467797769234</v>
+        <v>9.57133483581174e-10</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.340607170481235e-05</v>
+        <v>8.982776189547792e-10</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.107572643377353e-05</v>
+        <v>8.256144656826336e-10</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0001629798789508641</v>
+        <v>1.202193899985105e-11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.000124394049635157</v>
+        <v>5.916488410306897e-10</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.488929334911518e-06</v>
+        <v>1.26756138918438e-09</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0001109498407458887</v>
+        <v>1.476437416769727e-09</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0002674241550266743</v>
+        <v>7.486489761454607e-10</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.001241233432665467</v>
+        <v>8.269294138329997e-10</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.669861012487672e-05</v>
+        <v>1.522274861720518e-09</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.903766289819032e-05</v>
+        <v>1.203623589685066e-10</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0002355469187023118</v>
+        <v>3.40071570903433e-09</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.952719660243019e-05</v>
+        <v>2.92975554927466e-09</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0002837244537658989</v>
+        <v>2.286568989706694e-10</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.207908644573763e-05</v>
+        <v>1.605002020177437e-09</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0001902713265735656</v>
+        <v>2.471752247323877e-10</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.736156188300811e-05</v>
+        <v>1.275734518024763e-10</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.746713602798991e-05</v>
+        <v>1.914740366260048e-09</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.637438557139831e-07</v>
+        <v>3.21075943610083e-10</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0002844493428710848</v>
+        <v>3.993242625455196e-09</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.0008216357091441751</v>
+        <v>3.542489412922123e-09</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0003049129445571452</v>
+        <v>6.167321653371971e-10</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0004203994758427143</v>
+        <v>4.584823631859081e-10</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0001047820042003877</v>
+        <v>6.841798794177123e-10</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0002161597076337785</v>
+        <v>2.000394294654484e-10</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0001910929568111897</v>
+        <v>8.275307661342879e-10</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.255366992671043e-05</v>
+        <v>8.934695205908838e-10</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.743705332861282e-05</v>
+        <v>2.811484378639761e-10</v>
       </c>
       <c r="BO11" t="n">
-        <v>6.90043016220443e-05</v>
+        <v>2.795156051060843e-10</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0001220749691128731</v>
+        <v>1.47092549251937e-09</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0001842811907408759</v>
+        <v>9.667791567302686e-11</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0001578608062118292</v>
+        <v>4.143934917433256e-10</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0001009397747111507</v>
+        <v>2.496979290000922e-10</v>
       </c>
       <c r="BT11" t="n">
-        <v>1.783066909410991e-05</v>
+        <v>2.674609700381581e-10</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0002299016778124496</v>
+        <v>7.355069886472165e-10</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0007862353813834488</v>
+        <v>1.996231235867896e-10</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0002470333129167557</v>
+        <v>1.906571012177949e-10</v>
       </c>
       <c r="BX11" t="n">
-        <v>7.551360613433644e-05</v>
+        <v>3.485048361007159e-10</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.058032184024341e-05</v>
+        <v>2.258651043973714e-10</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0002563529415056109</v>
+        <v>2.855467418072521e-09</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0001374090934405103</v>
+        <v>1.745783795303879e-10</v>
       </c>
       <c r="CB11" t="n">
-        <v>2.703298014239408e-05</v>
+        <v>5.611465736521382e-10</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.971670255647041e-06</v>
+        <v>6.811316510813015e-10</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.480227365391329e-05</v>
+        <v>1.946675265429576e-09</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0002249443205073476</v>
+        <v>5.052612772615817e-10</v>
       </c>
       <c r="CF11" t="n">
-        <v>5.264060018816963e-05</v>
+        <v>4.4001341459321e-10</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0001273872767342255</v>
+        <v>7.207336394365882e-10</v>
       </c>
       <c r="CH11" t="n">
-        <v>9.881591540761292e-05</v>
+        <v>6.83898715436726e-10</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0001180034669232555</v>
+        <v>1.847786146313979e-09</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0001291388471145183</v>
+        <v>7.224597309285485e-11</v>
       </c>
       <c r="CK11" t="n">
-        <v>3.34826618200168e-05</v>
+        <v>6.716854294985808e-10</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.564936610520817e-05</v>
+        <v>5.036297490157438e-10</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0001803829363780096</v>
+        <v>1.420995321410601e-09</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0001714175741653889</v>
+        <v>1.347816858121575e-09</v>
       </c>
       <c r="CO11" t="n">
-        <v>2.139351636287756e-05</v>
+        <v>2.005958288364695e-09</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.789025504374877e-05</v>
+        <v>8.793925587724516e-10</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.3070140236523e-05</v>
+        <v>1.176492236965032e-10</v>
       </c>
       <c r="CR11" t="n">
-        <v>9.006159962154925e-05</v>
+        <v>1.685128259154567e-09</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0002702077617868781</v>
+        <v>2.80125589391389e-10</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0003373978252056986</v>
+        <v>4.307103285139391e-10</v>
       </c>
       <c r="CU11" t="n">
-        <v>5.523204526980408e-05</v>
+        <v>1.442112429472786e-09</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.830587279982865e-06</v>
+        <v>1.980642538867983e-09</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0001574330672156066</v>
+        <v>7.000384161237605e-10</v>
       </c>
       <c r="CX11" t="n">
-        <v>2.294676278324914e-06</v>
+        <v>5.178841244735111e-10</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0001531709858682007</v>
+        <v>7.301299009832007e-10</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0001193353382404894</v>
+        <v>2.406136956345506e-10</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0001925125980051234</v>
+        <v>2.06287009696382e-09</v>
       </c>
       <c r="DB11" t="n">
-        <v>9.939837036654353e-05</v>
+        <v>1.658929243975038e-10</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.457381040381733e-05</v>
+        <v>3.525014724559128e-10</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.421187309664674e-05</v>
+        <v>6.483548142810491e-10</v>
       </c>
       <c r="DE11" t="n">
-        <v>6.985255458857864e-05</v>
+        <v>1.352573941737489e-09</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.000324512307997793</v>
+        <v>2.759029449350692e-09</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0001066046461346559</v>
+        <v>1.17149179246212e-10</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0002176561392843723</v>
+        <v>4.849743939772111e-10</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0003616406465880573</v>
+        <v>1.184109921226195e-09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0001416091399732977</v>
+        <v>2.528421472192122e-09</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0003199028724338859</v>
+        <v>1.286388218169066e-09</v>
       </c>
       <c r="DL11" t="n">
-        <v>5.082532152300701e-05</v>
+        <v>1.301259766606222e-09</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0001751603558659554</v>
+        <v>7.406073532223445e-10</v>
       </c>
       <c r="DN11" t="n">
-        <v>5.745814996771514e-05</v>
+        <v>1.727657572558883e-09</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.676812644291203e-07</v>
+        <v>4.718656576585545e-10</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0001184039138024673</v>
+        <v>2.216169886493091e-10</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0004146515857428312</v>
+        <v>9.322367322539549e-10</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.852566679706797e-05</v>
+        <v>9.486545993198092e-10</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0004694777890108526</v>
+        <v>1.431662122186594e-09</v>
       </c>
       <c r="DT11" t="n">
-        <v>1.091982994694263e-05</v>
+        <v>1.817800909797995e-09</v>
       </c>
       <c r="DU11" t="n">
-        <v>2.933448195108213e-05</v>
+        <v>4.742113368649825e-10</v>
       </c>
       <c r="DV11" t="n">
-        <v>6.089181988500059e-05</v>
+        <v>1.665792503935393e-09</v>
       </c>
       <c r="DW11" t="n">
-        <v>4.907105903839692e-06</v>
+        <v>2.919700314851781e-10</v>
       </c>
       <c r="DX11" t="n">
-        <v>2.503696487110574e-05</v>
+        <v>9.05160724151699e-10</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.328686140477657e-05</v>
+        <v>2.457601233629703e-09</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0001626526500331238</v>
+        <v>2.19015516833565e-09</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.000140504096634686</v>
+        <v>1.100783575402886e-09</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0002250083634862676</v>
+        <v>2.391549180913444e-10</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0001180762264993973</v>
+        <v>1.261010740272184e-09</v>
       </c>
       <c r="ED11" t="n">
-        <v>9.354737267130986e-05</v>
+        <v>8.815311258736358e-10</v>
       </c>
       <c r="EE11" t="n">
-        <v>3.841397119686007e-05</v>
+        <v>1.013504502545004e-09</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.000138139323098585</v>
+        <v>2.502100304724308e-09</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0002189378865296021</v>
+        <v>1.654480996648999e-09</v>
       </c>
       <c r="EH11" t="n">
-        <v>1.019776027533226e-05</v>
+        <v>7.186169437289891e-10</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0001037688634824008</v>
+        <v>1.673878591290645e-09</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0002125711180269718</v>
+        <v>1.628572277034834e-10</v>
       </c>
       <c r="EK11" t="n">
-        <v>4.88130099256523e-05</v>
+        <v>1.009792360839867e-09</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0001647954777581617</v>
+        <v>2.600488435700044e-10</v>
       </c>
       <c r="EM11" t="n">
-        <v>9.59271528699901e-06</v>
+        <v>3.582906193955182e-10</v>
       </c>
       <c r="EN11" t="n">
-        <v>4.0073868149193e-05</v>
+        <v>4.438923950633722e-10</v>
       </c>
       <c r="EO11" t="n">
-        <v>5.984349991194904e-05</v>
+        <v>1.014129780152473e-09</v>
       </c>
       <c r="EP11" t="n">
-        <v>4.710055509349331e-05</v>
+        <v>9.137398615521874e-10</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0001742053718771785</v>
+        <v>1.507497571218153e-09</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.000121961158583872</v>
+        <v>2.092144235632531e-09</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0001586131111253053</v>
+        <v>3.612421473064842e-11</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0004084569809492677</v>
+        <v>3.102972323532072e-10</v>
       </c>
       <c r="EU11" t="n">
-        <v>6.717244104947895e-06</v>
+        <v>1.405235039442232e-09</v>
       </c>
       <c r="EV11" t="n">
-        <v>4.522484232438728e-06</v>
+        <v>1.184453535252317e-09</v>
       </c>
       <c r="EW11" t="n">
-        <v>5.656131179421209e-05</v>
+        <v>1.593884135786539e-09</v>
       </c>
       <c r="EX11" t="n">
-        <v>2.627175854286179e-05</v>
+        <v>2.258381925912545e-09</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0001748341019265354</v>
+        <v>8.507415882874625e-10</v>
       </c>
       <c r="EZ11" t="n">
-        <v>4.423105565365404e-05</v>
+        <v>2.448182767622598e-10</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0001567951985634863</v>
+        <v>9.507858944601821e-10</v>
       </c>
       <c r="FB11" t="n">
-        <v>5.69613475818187e-05</v>
+        <v>7.283743608255122e-10</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.000156582216732204</v>
+        <v>1.838796448438984e-09</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0001116265339078382</v>
+        <v>4.802966011019372e-11</v>
       </c>
       <c r="FE11" t="n">
-        <v>2.084299012494739e-06</v>
+        <v>3.695252992486076e-10</v>
       </c>
       <c r="FF11" t="n">
-        <v>2.500291157048196e-05</v>
+        <v>2.958505385119992e-10</v>
       </c>
       <c r="FG11" t="n">
-        <v>9.160196350421757e-05</v>
+        <v>5.490993215673257e-10</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0001368815283058211</v>
+        <v>6.911959893329822e-10</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0001620240946067497</v>
+        <v>2.260073905802074e-09</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0002500355476513505</v>
+        <v>1.87729831679917e-09</v>
       </c>
       <c r="FK11" t="n">
-        <v>4.976012132829055e-05</v>
+        <v>2.055635939246514e-10</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0001994353660847992</v>
+        <v>1.70161773560551e-09</v>
       </c>
       <c r="FM11" t="n">
-        <v>5.014377529732883e-05</v>
+        <v>2.091838507967125e-10</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0001025712917908095</v>
+        <v>9.447455318056797e-11</v>
       </c>
       <c r="FO11" t="n">
-        <v>2.751813008217141e-05</v>
+        <v>1.929919113408118e-09</v>
       </c>
       <c r="FP11" t="n">
-        <v>1.554222035338171e-05</v>
+        <v>1.140282535061488e-09</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0005355707253329456</v>
+        <v>8.81591910584234e-10</v>
       </c>
       <c r="FR11" t="n">
-        <v>5.269957182463259e-05</v>
+        <v>3.243358026594478e-09</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0003190279821865261</v>
+        <v>9.29421095641203e-10</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0001122289395425469</v>
+        <v>1.339781618980851e-09</v>
       </c>
       <c r="FU11" t="n">
-        <v>3.960415415349416e-05</v>
+        <v>2.294517242873439e-09</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0001621508417883888</v>
+        <v>8.577046295421553e-10</v>
       </c>
       <c r="FW11" t="n">
-        <v>8.433301991317421e-05</v>
+        <v>1.064015320295653e-09</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0001925833348650485</v>
+        <v>2.850096270101687e-10</v>
       </c>
       <c r="FY11" t="n">
-        <v>3.143020148854703e-05</v>
+        <v>3.882434373991828e-10</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0002090919442707673</v>
+        <v>3.857402175455604e-10</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0002273121353937313</v>
+        <v>1.466937904481824e-09</v>
       </c>
       <c r="GB11" t="n">
-        <v>4.044581874040887e-05</v>
+        <v>2.910374385933778e-09</v>
       </c>
       <c r="GC11" t="n">
-        <v>5.159938882570714e-05</v>
+        <v>3.477420573716472e-09</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0001490189752075821</v>
+        <v>2.043072155899495e-09</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.0001436555321561173</v>
+        <v>2.669497400908938e-10</v>
       </c>
       <c r="GF11" t="n">
-        <v>6.862070222268812e-06</v>
+        <v>5.262683622220266e-10</v>
       </c>
       <c r="GG11" t="n">
-        <v>2.326460889889859e-05</v>
+        <v>1.822372142079587e-09</v>
       </c>
     </row>
     <row r="12">
@@ -7258,571 +7258,571 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0003685256233438849</v>
+        <v>1.071582232725632e-06</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00548852514475584</v>
+        <v>2.074792973871808e-06</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0003503658517729491</v>
+        <v>8.366693293737626e-08</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001935375854372978</v>
+        <v>1.312944988285381e-07</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0006112621631473303</v>
+        <v>3.782213866543316e-07</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001210892107337713</v>
+        <v>7.756922286716872e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002183168398914859</v>
+        <v>1.975292605038703e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005196794518269598</v>
+        <v>3.054882142805582e-07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00117372116073966</v>
+        <v>2.411458694950852e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0006290130550041795</v>
+        <v>7.649384770047618e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0.005226342007517815</v>
+        <v>2.338048261663062e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0006838947301730514</v>
+        <v>7.418591962959908e-08</v>
       </c>
       <c r="M13" t="n">
-        <v>0.001995627535507083</v>
+        <v>2.932022766799491e-07</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0009334806818515062</v>
+        <v>8.847793537825055e-07</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001422218745574355</v>
+        <v>9.541981853544712e-07</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0005521342973224819</v>
+        <v>9.803920875128824e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0006828238256275654</v>
+        <v>1.357693975023722e-07</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0003049873048439622</v>
+        <v>7.288969072760665e-07</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001701921573840082</v>
+        <v>1.871121355634386e-07</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0003966421354562044</v>
+        <v>8.044810329010943e-08</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0008664525812491775</v>
+        <v>2.129993106336769e-07</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0002125328464899212</v>
+        <v>2.790764881410723e-07</v>
       </c>
       <c r="W13" t="n">
-        <v>4.244883893989027e-05</v>
+        <v>4.518087166616169e-07</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0001957906933967024</v>
+        <v>2.786211155125784e-07</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.00025647904840298</v>
+        <v>3.081388513237471e-07</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.646461169002578e-05</v>
+        <v>3.722793451288453e-07</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0003036850248463452</v>
+        <v>3.683471305748753e-08</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003223663661628962</v>
+        <v>8.550635755000258e-08</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.00102128810249269</v>
+        <v>2.42890962454112e-07</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001118921092711389</v>
+        <v>1.630904762350838e-07</v>
       </c>
       <c r="AE13" t="n">
-        <v>9.92530258372426e-05</v>
+        <v>8.540631029063661e-07</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0002934599760919809</v>
+        <v>7.969025546117336e-07</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.298860636074096e-05</v>
+        <v>1.194853496144788e-07</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0002826025011017919</v>
+        <v>2.440659443436743e-07</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0001516940974397585</v>
+        <v>5.635298521156074e-07</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0003178164479322731</v>
+        <v>1.701500167428094e-07</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0004942358937114477</v>
+        <v>4.548441268070746e-07</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0004543442628346384</v>
+        <v>2.492980115675891e-07</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0009302415419369936</v>
+        <v>2.35389492786453e-07</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0001553944748593494</v>
+        <v>5.574769943450519e-07</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0003510176902636886</v>
+        <v>8.918362937038182e-09</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0004390909743960947</v>
+        <v>2.417350515315775e-07</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0006742172408849001</v>
+        <v>3.320910764159635e-07</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0001775053824530914</v>
+        <v>9.606155515484716e-08</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0001978870423045009</v>
+        <v>9.345940554794652e-08</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0005355636822059751</v>
+        <v>6.210174774423649e-07</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.004737746901810169</v>
+        <v>1.578813453306793e-06</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.00146492337808013</v>
+        <v>2.952191380245495e-09</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.806040179682896e-05</v>
+        <v>1.668896203455006e-07</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001876441179774702</v>
+        <v>7.516696314269211e-07</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0001883773074951023</v>
+        <v>5.725358391828195e-07</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0004249799530953169</v>
+        <v>6.471367441918119e-08</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.986438292078674e-05</v>
+        <v>3.641622470240691e-07</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0006071306997910142</v>
+        <v>2.477364375863544e-07</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0002389979345025495</v>
+        <v>3.399097749934299e-07</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.00106169655919075</v>
+        <v>4.501368380260828e-07</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0006379771512001753</v>
+        <v>3.537233226325043e-07</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.849965913919732e-05</v>
+        <v>2.750135408291499e-08</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0005761414649896324</v>
+        <v>3.804549919550482e-07</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.001571185071952641</v>
+        <v>3.007121449627448e-07</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001265097671421245</v>
+        <v>2.178108502448595e-07</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0004314145771786571</v>
+        <v>3.027633113106276e-07</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0005559867131523788</v>
+        <v>3.168801043784697e-08</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0006668514688499272</v>
+        <v>7.05801284084373e-08</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.000189392187166959</v>
+        <v>1.405715011060238e-07</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0001234108931384981</v>
+        <v>9.180112670037488e-09</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.000369964400306344</v>
+        <v>9.972072945174659e-08</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0006757783703505993</v>
+        <v>4.055842737216153e-07</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0004288837953936309</v>
+        <v>1.12797906126616e-07</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.00062644446734339</v>
+        <v>4.471172587727779e-07</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0005091400817036629</v>
+        <v>1.682509207512339e-07</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001894852466648445</v>
+        <v>3.765726432902738e-07</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0003048338112421334</v>
+        <v>7.540648994108778e-07</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.002040222520008683</v>
+        <v>8.791892582848959e-07</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.000823156675323844</v>
+        <v>1.080950724485774e-07</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0002317886101081967</v>
+        <v>1.534378668566205e-07</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.001093362225219607</v>
+        <v>1.382463210575224e-07</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003729015006683767</v>
+        <v>5.974229679850396e-07</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.00033877621171996</v>
+        <v>3.322073212075338e-07</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0002295585436513647</v>
+        <v>1.000878171453223e-07</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.672328188666143e-05</v>
+        <v>7.468840124147391e-08</v>
       </c>
       <c r="CD13" t="n">
-        <v>8.284372597699985e-05</v>
+        <v>3.061842619445088e-07</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0008947089081630111</v>
+        <v>6.155739242785785e-07</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001221321726916358</v>
+        <v>8.410555807358833e-08</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.400069570285268e-05</v>
+        <v>9.613386708906546e-08</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0002459728566464037</v>
+        <v>6.528289731022596e-08</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002142053854186088</v>
+        <v>2.486824826064549e-07</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002973259252030402</v>
+        <v>1.292009983444586e-07</v>
       </c>
       <c r="CK13" t="n">
-        <v>2.801868868118618e-05</v>
+        <v>6.531605833970389e-08</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.492826752131805e-05</v>
+        <v>1.068513881818944e-07</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0007137333159334958</v>
+        <v>1.172956842765416e-07</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001174024422653019</v>
+        <v>8.334449717040116e-07</v>
       </c>
       <c r="CO13" t="n">
-        <v>8.805612742435187e-05</v>
+        <v>3.507287829052075e-07</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001539605902507901</v>
+        <v>1.990830185150116e-07</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.001385051757097244</v>
+        <v>3.111977946446132e-07</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0004211400810163468</v>
+        <v>5.78320339172933e-07</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0006350934854708612</v>
+        <v>1.388381178912823e-07</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001475891447626054</v>
+        <v>4.00018365098731e-08</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0004048672853969038</v>
+        <v>2.141050714499215e-07</v>
       </c>
       <c r="CV13" t="n">
-        <v>4.847351010539569e-05</v>
+        <v>2.348451317857325e-07</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0008437571232207119</v>
+        <v>5.835416345689737e-07</v>
       </c>
       <c r="CX13" t="n">
-        <v>8.464956044917926e-05</v>
+        <v>9.932939804002672e-08</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0001663009024923667</v>
+        <v>7.641225607812885e-08</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0002711488923523575</v>
+        <v>6.934954654980174e-08</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0004095601907465607</v>
+        <v>2.688672680051241e-07</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0002492254134267569</v>
+        <v>9.512954868284851e-09</v>
       </c>
       <c r="DC13" t="n">
-        <v>9.265430708182976e-05</v>
+        <v>1.95034672856309e-07</v>
       </c>
       <c r="DD13" t="n">
-        <v>9.037769632413983e-05</v>
+        <v>7.18185475534483e-08</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.000366765249054879</v>
+        <v>2.583944080924994e-08</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0004239487461745739</v>
+        <v>2.936618557214388e-07</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0003252035530749708</v>
+        <v>6.673768382370326e-08</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0009329678723588586</v>
+        <v>1.549474859530164e-07</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0009051450761035085</v>
+        <v>7.141455284909171e-07</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0005998869310133159</v>
+        <v>4.730844693767722e-08</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.000231764410273172</v>
+        <v>2.03373133444984e-07</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0004039049381390214</v>
+        <v>2.245354693286572e-07</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0002965579042211175</v>
+        <v>3.010075033671455e-07</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001770905364537612</v>
+        <v>3.466190179324258e-08</v>
       </c>
       <c r="DO13" t="n">
-        <v>7.518283382523805e-06</v>
+        <v>4.86519070364011e-07</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001256922696484253</v>
+        <v>2.265654188704502e-07</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0004553420876618475</v>
+        <v>1.505434852333565e-07</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0003483712498564273</v>
+        <v>2.530518372623192e-07</v>
       </c>
       <c r="DS13" t="n">
-        <v>5.880474418518133e-06</v>
+        <v>4.346969433299819e-07</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0001581418036948889</v>
+        <v>1.07520591541288e-07</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0002264998765895143</v>
+        <v>4.388618890516227e-07</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0001089398501790129</v>
+        <v>3.419374934310326e-07</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0001074503816198558</v>
+        <v>2.733406461175036e-07</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0002630185626912862</v>
+        <v>3.878037659887923e-07</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0001964211405720562</v>
+        <v>6.190121837335028e-08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0001299282012041658</v>
+        <v>2.763671886896191e-07</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0004576818319037557</v>
+        <v>6.168028221509303e-08</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0002741302305366844</v>
+        <v>2.039302273715293e-07</v>
       </c>
       <c r="EC13" t="n">
-        <v>4.35989277320914e-05</v>
+        <v>1.962698448210176e-08</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0008801391231827438</v>
+        <v>4.82803613977012e-07</v>
       </c>
       <c r="EE13" t="n">
-        <v>9.16886783670634e-05</v>
+        <v>1.221441436882742e-07</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002151339867850766</v>
+        <v>3.248524649279716e-07</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.001087434240616858</v>
+        <v>5.69395304239606e-08</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0003613869484979659</v>
+        <v>1.754972913659003e-07</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0005143521702848375</v>
+        <v>7.187995265667269e-08</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0006363834836520255</v>
+        <v>9.323983363174193e-08</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0001128023432102054</v>
+        <v>1.234105866387836e-07</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001599125098437071</v>
+        <v>3.616597510358588e-08</v>
       </c>
       <c r="EM13" t="n">
-        <v>1.861640157585498e-06</v>
+        <v>1.023815912049031e-07</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0001267260377062485</v>
+        <v>6.632512139503888e-08</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0002630534581840038</v>
+        <v>3.263400287778495e-07</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.001117897569201887</v>
+        <v>1.101928432944987e-07</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0004422441124916077</v>
+        <v>1.689887909606114e-07</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.000285306537989527</v>
+        <v>7.550509195652921e-08</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.000614642514847219</v>
+        <v>4.113283011975e-07</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0006349085597321391</v>
+        <v>4.761807304021204e-07</v>
       </c>
       <c r="EU13" t="n">
-        <v>9.591397974872962e-05</v>
+        <v>1.390844488469156e-07</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.00032469053985551</v>
+        <v>6.053814161077753e-08</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0004465346282813698</v>
+        <v>2.723298564433208e-07</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001231686910614371</v>
+        <v>3.029799131581967e-07</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0007943430682644248</v>
+        <v>6.686580604764458e-07</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0002549689379520714</v>
+        <v>4.068770564913393e-08</v>
       </c>
       <c r="FA13" t="n">
-        <v>3.791672861552797e-05</v>
+        <v>5.361687982485819e-08</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001230116322403774</v>
+        <v>2.242942009900162e-08</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0002669685345608741</v>
+        <v>2.111841581609042e-07</v>
       </c>
       <c r="FD13" t="n">
-        <v>7.268775516422465e-05</v>
+        <v>1.51746149867904e-07</v>
       </c>
       <c r="FE13" t="n">
-        <v>7.416451262542978e-05</v>
+        <v>1.19518318797418e-07</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0001037485199049115</v>
+        <v>7.339313157217475e-09</v>
       </c>
       <c r="FG13" t="n">
-        <v>7.146678399294615e-05</v>
+        <v>2.427985457131854e-08</v>
       </c>
       <c r="FH13" t="n">
-        <v>6.681623199256137e-05</v>
+        <v>4.006824667612818e-07</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0003355004591867328</v>
+        <v>2.92351074904218e-07</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0006145680672489107</v>
+        <v>2.04669234449284e-07</v>
       </c>
       <c r="FK13" t="n">
-        <v>2.335000317543745e-07</v>
+        <v>8.322992073317437e-09</v>
       </c>
       <c r="FL13" t="n">
-        <v>1.508253444626462e-05</v>
+        <v>4.714945305295259e-07</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0005636339192278683</v>
+        <v>1.237607705206756e-07</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0005223033367656171</v>
+        <v>1.34264681150853e-07</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0001184260472655296</v>
+        <v>3.317810524094966e-07</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0006096466677263379</v>
+        <v>6.750274224032182e-07</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.001800489029847085</v>
+        <v>7.531081678280316e-07</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0005423270049504936</v>
+        <v>1.930359445623253e-07</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0007293292437680066</v>
+        <v>5.944139616076427e-07</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.001628794707357883</v>
+        <v>3.096781142630789e-08</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001012749737128615</v>
+        <v>5.952994683866564e-07</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0002788587298709899</v>
+        <v>3.127940431113529e-07</v>
       </c>
       <c r="FW13" t="n">
-        <v>1.406791852787137e-06</v>
+        <v>2.911255876369978e-07</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0005829363944940269</v>
+        <v>1.970429082120972e-07</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0001832182169891894</v>
+        <v>3.523520604176156e-07</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0007145041599869728</v>
+        <v>8.858499711550394e-09</v>
       </c>
       <c r="GA13" t="n">
-        <v>4.880791493633296e-06</v>
+        <v>2.907282237174513e-07</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0006711768801324069</v>
+        <v>1.639712934320414e-07</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0004426340165082365</v>
+        <v>2.050374234841001e-07</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0003948589728679508</v>
+        <v>4.361783396689134e-07</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0001509324065409601</v>
+        <v>3.709859299760865e-07</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0001328701328020543</v>
+        <v>1.093144419428427e-07</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0007310268701985478</v>
+        <v>3.989503056800459e-07</v>
       </c>
     </row>
     <row r="14">
@@ -8396,571 +8396,571 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0007232131902128458</v>
+        <v>0.01385347917675972</v>
       </c>
       <c r="B15" t="n">
-        <v>0.07323697209358215</v>
+        <v>0.820382833480835</v>
       </c>
       <c r="C15" t="n">
-        <v>0.009332195855677128</v>
+        <v>0.07605451345443726</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03504924103617668</v>
+        <v>0.3075952529907227</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03907980024814606</v>
+        <v>0.1295354664325714</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02990692853927612</v>
+        <v>0.4866538643836975</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01423895452171564</v>
+        <v>0.05846915394067764</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02402032166719437</v>
+        <v>0.1066431552171707</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001835681730881333</v>
+        <v>0.1281065791845322</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0008072894997894764</v>
+        <v>0.1855143308639526</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06137196347117424</v>
+        <v>0.9423661231994629</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003436010796576738</v>
+        <v>0.07180631160736084</v>
       </c>
       <c r="M15" t="n">
-        <v>0.02113978937268257</v>
+        <v>0.5605049133300781</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02477126754820347</v>
+        <v>0.1328899562358856</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02941547520458698</v>
+        <v>0.4346943795681</v>
       </c>
       <c r="P15" t="n">
-        <v>0.01300888508558273</v>
+        <v>0.1443999856710434</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.004631909541785717</v>
+        <v>0.1686467975378036</v>
       </c>
       <c r="R15" t="n">
-        <v>0.003752089571207762</v>
+        <v>0.1453820466995239</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001470937277190387</v>
+        <v>0.08127311617136002</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01161795295774937</v>
+        <v>0.2312881052494049</v>
       </c>
       <c r="U15" t="n">
-        <v>0.001025028061121702</v>
+        <v>0.02580677159130573</v>
       </c>
       <c r="V15" t="n">
-        <v>0.01237614452838898</v>
+        <v>0.1404941976070404</v>
       </c>
       <c r="W15" t="n">
-        <v>0.009779474698007107</v>
+        <v>0.03124493174254894</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002558631589636207</v>
+        <v>0.03716154024004936</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.005269096232950687</v>
+        <v>0.04780488833785057</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.01102349441498518</v>
+        <v>0.04639687389135361</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.006451552733778954</v>
+        <v>0.04518020153045654</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.004477008245885372</v>
+        <v>0.0524611622095108</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.00576293095946312</v>
+        <v>0.0516737587749958</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.002322602085769176</v>
+        <v>0.08177242428064346</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.005636401008814573</v>
+        <v>0.1297238767147064</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.006834377534687519</v>
+        <v>0.2162785530090332</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.00496002659201622</v>
+        <v>0.00604952871799469</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.008293246850371361</v>
+        <v>0.07343363761901855</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.008338660933077335</v>
+        <v>0.2761081159114838</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.003816619981080294</v>
+        <v>0.04913420230150223</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.006512521766126156</v>
+        <v>0.04194799065589905</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01823567971587181</v>
+        <v>0.2523787319660187</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.002584610600024462</v>
+        <v>0.002784254029393196</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.003697742242366076</v>
+        <v>0.04792205989360809</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.001033389125950634</v>
+        <v>0.1423359215259552</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.01373051293194294</v>
+        <v>0.1717696040868759</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0006689894944429398</v>
+        <v>0.09517192095518112</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.009864936582744122</v>
+        <v>0.3009786605834961</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.00747118704020977</v>
+        <v>0.01442037988454103</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.005787738598883152</v>
+        <v>0.07653211057186127</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.05509481579065323</v>
+        <v>0.8325841426849365</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.000830640085041523</v>
+        <v>0.001679226756095886</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.003879271680489182</v>
+        <v>0.1159069463610649</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.01087738573551178</v>
+        <v>0.0103595182299614</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01630708016455173</v>
+        <v>0.2284907251596451</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.002000659937039018</v>
+        <v>0.08604785799980164</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0139271579682827</v>
+        <v>0.018988236784935</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.003385134972631931</v>
+        <v>0.09029976278543472</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0003292891196906567</v>
+        <v>0.06222575902938843</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.008661854080855846</v>
+        <v>0.1588167101144791</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.007805638946592808</v>
+        <v>0.1260969787836075</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.008548934012651443</v>
+        <v>0.111993245780468</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.02081038057804108</v>
+        <v>0.2474537193775177</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.003732822835445404</v>
+        <v>0.1414233446121216</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.01327074877917767</v>
+        <v>0.04269204288721085</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.012590067461133</v>
+        <v>0.09635801613330841</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.003749889554455876</v>
+        <v>0.1402001976966858</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.009532762691378593</v>
+        <v>0.1134670227766037</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0115637443959713</v>
+        <v>0.02299496904015541</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.003474289085716009</v>
+        <v>0.04135503992438316</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.003604021389037371</v>
+        <v>0.06106346845626831</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.002366311615332961</v>
+        <v>0.05425621941685677</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.006875894498080015</v>
+        <v>0.1031157597899437</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.003566626459360123</v>
+        <v>0.1753068417310715</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.005741163156926632</v>
+        <v>0.09307581931352615</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.007002085447311401</v>
+        <v>0.07226714491844177</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.006812591571360826</v>
+        <v>0.1095993593335152</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.03491942957043648</v>
+        <v>0.6698492169380188</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.01311877556145191</v>
+        <v>0.02788223326206207</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.004204056225717068</v>
+        <v>0.2067789733409882</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.008220972493290901</v>
+        <v>0.07719158381223679</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.002191991545259953</v>
+        <v>0.1149242669343948</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.003524231957271695</v>
+        <v>0.1008457988500595</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.003626296995207667</v>
+        <v>0.01271705236285925</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.006016177125275135</v>
+        <v>0.0012122867628932</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.002028041053563356</v>
+        <v>0.005141805857419968</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.01014235615730286</v>
+        <v>0.2530069649219513</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.002535735722631216</v>
+        <v>0.01594003476202488</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.005896788090467453</v>
+        <v>0.02394979074597359</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.001846517785452306</v>
+        <v>0.06648662686347961</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.005169836804270744</v>
+        <v>0.09785216301679611</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.004077254328876734</v>
+        <v>0.01789109781384468</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.004216906614601612</v>
+        <v>0.04804365336894989</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.003804543521255255</v>
+        <v>0.02388945408165455</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.008372101932764053</v>
+        <v>0.1262245625257492</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.005565297789871693</v>
+        <v>0.3504915535449982</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0001307912170886993</v>
+        <v>0.00244604516774416</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.009431169368326664</v>
+        <v>0.1132896021008492</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.009866555221378803</v>
+        <v>0.1163364946842194</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.004935581237077713</v>
+        <v>0.003770653158426285</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.01467872504144907</v>
+        <v>0.03611505031585693</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.01483918819576502</v>
+        <v>0.1975916028022766</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.001548848696984351</v>
+        <v>0.02144400775432587</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.00202804640866816</v>
+        <v>0.04871054738759995</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.008618553169071674</v>
+        <v>0.2608991861343384</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.003293181536719203</v>
+        <v>0.005459161475300789</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.008700260892510414</v>
+        <v>0.03466533496975899</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.001340007525868714</v>
+        <v>0.07819946110248566</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.00907435454428196</v>
+        <v>0.1143166869878769</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.003103140508756042</v>
+        <v>0.01471762079745531</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.005464321933686733</v>
+        <v>0.03142532706260681</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0009085648925974965</v>
+        <v>0.02222326956689358</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.003284411272034049</v>
+        <v>0.0796862468123436</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.008281569927930832</v>
+        <v>0.328600287437439</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.003406904870644212</v>
+        <v>0.2250547707080841</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.02576043829321861</v>
+        <v>0.00401512673124671</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01100722700357437</v>
+        <v>0.2284659147262573</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.003726084250956774</v>
+        <v>0.2772091031074524</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.01260572671890259</v>
+        <v>0.05773026496171951</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.006388726644217968</v>
+        <v>0.0812721848487854</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.007457803469151258</v>
+        <v>0.1580039709806442</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.00201886729337275</v>
+        <v>0.01921744644641876</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.006989662069827318</v>
+        <v>0.1684867143630981</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.00460658548399806</v>
+        <v>0.02651140280067921</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.005305519327521324</v>
+        <v>0.1193765103816986</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0007051688153296709</v>
+        <v>0.06467391550540924</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.008943047374486923</v>
+        <v>0.07944650202989578</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.00282702874392271</v>
+        <v>0.0002145115286111832</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.003905817167833447</v>
+        <v>0.03879018872976303</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.003172978525981307</v>
+        <v>0.009191062301397324</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.003830681322142482</v>
+        <v>0.1041234135627747</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.002291380893439054</v>
+        <v>0.09566551446914673</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.008718498051166534</v>
+        <v>0.01231788098812103</v>
       </c>
       <c r="DZ15" t="n">
-        <v>9.98261384665966e-05</v>
+        <v>0.03352492675185204</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.005418511107563972</v>
+        <v>0.03727772831916809</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.006144034210592508</v>
+        <v>0.09114846587181091</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0003257442731410265</v>
+        <v>0.02355768159031868</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.005076531320810318</v>
+        <v>0.06221185252070427</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0001260429853573442</v>
+        <v>0.2288725078105927</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.002025339286774397</v>
+        <v>0.05903680995106697</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.00987965427339077</v>
+        <v>0.08992747962474823</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.00417507765814662</v>
+        <v>0.04015081003308296</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.003055643057450652</v>
+        <v>0.1234199330210686</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01095179095864296</v>
+        <v>0.1418476104736328</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.004819945897907019</v>
+        <v>0.01587668061256409</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.004992373287677765</v>
+        <v>0.0311281681060791</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.002924009459093213</v>
+        <v>0.05412626639008522</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0001331319799646735</v>
+        <v>0.009556474164128304</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.0003072270192205906</v>
+        <v>0.08976231515407562</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.002828328870236874</v>
+        <v>0.161364808678627</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.009562257677316666</v>
+        <v>0.02759883180260658</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.008943933062255383</v>
+        <v>0.01304362714290619</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.005487105809152126</v>
+        <v>0.1748634874820709</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.01350124645978212</v>
+        <v>0.02110873721539974</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.004083711188286543</v>
+        <v>0.02220677770674229</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.01268477737903595</v>
+        <v>0.02123962715268135</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.00130204507149756</v>
+        <v>0.01231794152408838</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.001483271713368595</v>
+        <v>0.00461505725979805</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.007739189546555281</v>
+        <v>0.2786702513694763</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.002272582147270441</v>
+        <v>0.02884087339043617</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.007827014662325382</v>
+        <v>0.02824859879910946</v>
       </c>
       <c r="FB15" t="n">
-        <v>1.636327942833304e-05</v>
+        <v>0.08997447788715363</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.006114540621638298</v>
+        <v>0.09267577528953552</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.005261032842099667</v>
+        <v>0.02319201827049255</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.005188500508666039</v>
+        <v>0.02043864689767361</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.003815019503235817</v>
+        <v>0.04338761419057846</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.002184635959565639</v>
+        <v>0.04711943119764328</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.006319383159279823</v>
+        <v>0.1600345373153687</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.009481464512646198</v>
+        <v>0.02607860416173935</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.01087071746587753</v>
+        <v>0.02144878357648849</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.002307700924575329</v>
+        <v>0.09582120180130005</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.0003116352017968893</v>
+        <v>0.1336044371128082</v>
       </c>
       <c r="FM15" t="n">
-        <v>1.612585037946701e-05</v>
+        <v>0.0622415766119957</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.003442005719989538</v>
+        <v>0.1074658706784248</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.005069048143923283</v>
+        <v>0.1327780038118362</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0002755799796432257</v>
+        <v>0.0705939307808876</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01091440580785275</v>
+        <v>0.2197619378566742</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.01026723347604275</v>
+        <v>9.468942880630493e-05</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.01144157256931067</v>
+        <v>0.2309572696685791</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.007495467085391283</v>
+        <v>0.0982951819896698</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0003429681528359652</v>
+        <v>0.05211995542049408</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.008480323478579521</v>
+        <v>0.1687512248754501</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.004465073347091675</v>
+        <v>0.08162209391593933</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.0004247609758749604</v>
+        <v>0.04105102270841599</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.01021525263786316</v>
+        <v>0.1124769225716591</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.001777382218278944</v>
+        <v>0.156213715672493</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.00111219403333962</v>
+        <v>0.009439803659915924</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.006465183105319738</v>
+        <v>0.05046334117650986</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.007010583765804768</v>
+        <v>0.06591905653476715</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.008239729329943657</v>
+        <v>0.02340422570705414</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0301455594599247</v>
+        <v>0.08386961370706558</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.002685714513063431</v>
+        <v>0.02634806558489799</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0004237866960465908</v>
+        <v>0.04713568091392517</v>
       </c>
     </row>
     <row r="16">
